--- a/flagship_dashboard.xlsx
+++ b/flagship_dashboard.xlsx
@@ -1,19 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agrosko\Dropbox\Coding\srn\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4812D243-AAA8-4D74-8F1B-D61173D7F5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$HD$135</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8252" uniqueCount="1342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8252" uniqueCount="1342">
   <si>
     <t>publication_date_2025</t>
   </si>
@@ -2859,9 +2869,6 @@
     <t>2026-02-24T10:05:47.530818+00:00</t>
   </si>
   <si>
-    <t>sector</t>
-  </si>
-  <si>
     <t>Food &amp; Beverage</t>
   </si>
   <si>
@@ -4039,13 +4046,16 @@
   </si>
   <si>
     <t>Extractives</t>
+  </si>
+  <si>
+    <t>primary_sics_sector</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4067,29 +4077,366 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:HD135"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4613,121 +4960,121 @@
         <v>943</v>
       </c>
       <c r="FS1" t="s">
-        <v>948</v>
+        <v>1341</v>
       </c>
       <c r="FT1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="FU1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="FV1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="FW1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="FX1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="FY1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="FZ1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="GA1" t="s">
         <v>1196</v>
       </c>
-      <c r="GA1" t="s">
+      <c r="GB1" t="s">
         <v>1197</v>
       </c>
-      <c r="GB1" t="s">
-        <v>1198</v>
-      </c>
       <c r="GC1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="GD1" t="s">
         <v>1308</v>
       </c>
-      <c r="GD1" t="s">
+      <c r="GE1" t="s">
         <v>1309</v>
       </c>
-      <c r="GE1" t="s">
+      <c r="GF1" t="s">
         <v>1310</v>
       </c>
-      <c r="GF1" t="s">
+      <c r="GG1" t="s">
         <v>1311</v>
       </c>
-      <c r="GG1" t="s">
+      <c r="GH1" t="s">
         <v>1312</v>
       </c>
-      <c r="GH1" t="s">
+      <c r="GI1" t="s">
         <v>1313</v>
       </c>
-      <c r="GI1" t="s">
+      <c r="GJ1" t="s">
         <v>1314</v>
       </c>
-      <c r="GJ1" t="s">
+      <c r="GK1" t="s">
         <v>1315</v>
       </c>
-      <c r="GK1" t="s">
+      <c r="GL1" t="s">
         <v>1316</v>
       </c>
-      <c r="GL1" t="s">
+      <c r="GM1" t="s">
         <v>1317</v>
       </c>
-      <c r="GM1" t="s">
+      <c r="GN1" t="s">
         <v>1318</v>
       </c>
-      <c r="GN1" t="s">
+      <c r="GO1" t="s">
         <v>1319</v>
       </c>
-      <c r="GO1" t="s">
+      <c r="GP1" t="s">
         <v>1320</v>
       </c>
-      <c r="GP1" t="s">
+      <c r="GQ1" t="s">
         <v>1321</v>
       </c>
-      <c r="GQ1" t="s">
+      <c r="GR1" t="s">
         <v>1322</v>
       </c>
-      <c r="GR1" t="s">
+      <c r="GS1" t="s">
         <v>1323</v>
       </c>
-      <c r="GS1" t="s">
+      <c r="GT1" t="s">
         <v>1324</v>
       </c>
-      <c r="GT1" t="s">
+      <c r="GU1" t="s">
         <v>1325</v>
       </c>
-      <c r="GU1" t="s">
+      <c r="GV1" t="s">
         <v>1326</v>
       </c>
-      <c r="GV1" t="s">
+      <c r="GW1" t="s">
         <v>1327</v>
       </c>
-      <c r="GW1" t="s">
+      <c r="GX1" t="s">
         <v>1328</v>
       </c>
-      <c r="GX1" t="s">
+      <c r="GY1" t="s">
         <v>1329</v>
       </c>
-      <c r="GY1" t="s">
+      <c r="GZ1" t="s">
         <v>1330</v>
       </c>
-      <c r="GZ1" t="s">
+      <c r="HA1" t="s">
         <v>1331</v>
       </c>
-      <c r="HA1" t="s">
+      <c r="HB1" t="s">
         <v>1332</v>
       </c>
-      <c r="HB1" t="s">
+      <c r="HC1" t="s">
         <v>1333</v>
       </c>
-      <c r="HC1" t="s">
-        <v>1334</v>
-      </c>
       <c r="HD1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -5207,32 +5554,32 @@
         <v>944</v>
       </c>
       <c r="FS2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="FT2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="FU2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="FV2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="FW2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="FX2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="FY2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="FZ2" s="1"/>
       <c r="GA2" s="1">
         <v>2024</v>
       </c>
       <c r="GB2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="GC2" t="s">
         <v>941</v>
@@ -5280,7 +5627,7 @@
         <v>0.31099998950958252</v>
       </c>
       <c r="GR2" s="1">
-        <v>0.078000001609325409</v>
+        <v>7.8000001609325409E-2</v>
       </c>
       <c r="GS2" s="1">
         <v>138.47099304199219</v>
@@ -5295,7 +5642,7 @@
         <v>0.89099997282028198</v>
       </c>
       <c r="GW2" s="1">
-        <v>0.037000000476837158</v>
+        <v>3.7000000476837158E-2</v>
       </c>
       <c r="GX2" s="1">
         <v>18.432703018188477</v>
@@ -5307,7 +5654,7 @@
         <v>2</v>
       </c>
       <c r="HA2" s="1">
-        <v>0.054054055362939835</v>
+        <v>5.4054055362939835E-2</v>
       </c>
       <c r="HB2" s="1">
         <v>1</v>
@@ -5316,10 +5663,10 @@
         <v>46</v>
       </c>
       <c r="HD2" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5645,32 +5992,32 @@
         <v>944</v>
       </c>
       <c r="FS3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="FT3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="FU3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="FV3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="FW3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="FX3" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="FY3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="FZ3" s="1"/>
       <c r="GA3" s="1">
         <v>2025</v>
       </c>
       <c r="GB3" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="GC3" t="s">
         <v>941</v>
@@ -5712,13 +6059,13 @@
         <v>0.20299999415874481</v>
       </c>
       <c r="GP3" s="1">
-        <v>0.23600000143051148</v>
+        <v>0.23600000143051147</v>
       </c>
       <c r="GQ3" s="1">
         <v>0.30399999022483826</v>
       </c>
       <c r="GR3" s="1">
-        <v>0.079000003635883331</v>
+        <v>7.9000003635883331E-2</v>
       </c>
       <c r="GS3" s="1">
         <v>132.7550048828125</v>
@@ -5733,7 +6080,7 @@
         <v>0.84500002861022949</v>
       </c>
       <c r="GW3" s="1">
-        <v>0.02500000037252903</v>
+        <v>2.500000037252903E-2</v>
       </c>
       <c r="GX3" s="1">
         <v>24.627838134765625</v>
@@ -5745,7 +6092,7 @@
         <v>3</v>
       </c>
       <c r="HA3" s="1">
-        <v>0.081081077456474304</v>
+        <v>8.1081077456474304E-2</v>
       </c>
       <c r="HB3" s="1">
         <v>1</v>
@@ -5754,10 +6101,10 @@
         <v>46</v>
       </c>
       <c r="HD3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6083,32 +6430,32 @@
         <v>944</v>
       </c>
       <c r="FS4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="FU4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="FV4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="FW4" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="FX4" t="s">
         <v>47</v>
       </c>
       <c r="FY4" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="FZ4" s="1"/>
       <c r="GA4" s="1">
         <v>2025</v>
       </c>
       <c r="GB4" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="GC4" t="s">
         <v>941</v>
@@ -6147,7 +6494,7 @@
         <v>111</v>
       </c>
       <c r="GO4" s="1">
-        <v>1.5670000314712525</v>
+        <v>1.5670000314712524</v>
       </c>
       <c r="GP4" s="1">
         <v>1.7539999485015869</v>
@@ -6168,7 +6515,7 @@
         <v>28.131999969482422</v>
       </c>
       <c r="GV4" s="1">
-        <v>4.4840002059936524</v>
+        <v>4.4840002059936523</v>
       </c>
       <c r="GW4" s="1">
         <v>0.11100000143051147</v>
@@ -6183,7 +6530,7 @@
         <v>12</v>
       </c>
       <c r="HA4" s="1">
-        <v>0.059113301336765289</v>
+        <v>5.9113301336765289E-2</v>
       </c>
       <c r="HB4" s="1">
         <v>2</v>
@@ -6192,10 +6539,10 @@
         <v>47</v>
       </c>
       <c r="HD4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -6675,32 +7022,32 @@
         <v>944</v>
       </c>
       <c r="FS5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="FU5" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="FV5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="FW5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="FX5" t="s">
         <v>47</v>
       </c>
       <c r="FY5" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="FZ5" s="1"/>
       <c r="GA5" s="1">
         <v>2024</v>
       </c>
       <c r="GB5" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="GC5" t="s">
         <v>941</v>
@@ -6745,7 +7092,7 @@
         <v>1.4290000200271606</v>
       </c>
       <c r="GQ5" s="1">
-        <v>1.1089999675750733</v>
+        <v>1.1089999675750732</v>
       </c>
       <c r="GR5" s="1">
         <v>0.32199999690055847</v>
@@ -6763,7 +7110,7 @@
         <v>2.7929999828338623</v>
       </c>
       <c r="GW5" s="1">
-        <v>0.019999999552965164</v>
+        <v>1.9999999552965164E-2</v>
       </c>
       <c r="GX5" s="1">
         <v>19.328742980957031</v>
@@ -6775,7 +7122,7 @@
         <v>15</v>
       </c>
       <c r="HA5" s="1">
-        <v>0.094339624047279358</v>
+        <v>9.4339624047279358E-2</v>
       </c>
       <c r="HB5" s="1">
         <v>2</v>
@@ -6784,10 +7131,10 @@
         <v>47</v>
       </c>
       <c r="HD5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -7285,32 +7632,32 @@
         <v>944</v>
       </c>
       <c r="FS6" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT6" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU6" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="FV6" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="FW6" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="FX6" t="s">
         <v>48</v>
       </c>
       <c r="FY6" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="FZ6" s="1"/>
       <c r="GA6" s="1">
         <v>2025</v>
       </c>
       <c r="GB6" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="GC6" t="s">
         <v>941</v>
@@ -7373,7 +7720,7 @@
         <v>2.6429998874664307</v>
       </c>
       <c r="GW6" s="1">
-        <v>0.054000001400709152</v>
+        <v>5.4000001400709152E-2</v>
       </c>
       <c r="GX6" s="1">
         <v>21.252658843994141</v>
@@ -7385,7 +7732,7 @@
         <v>14</v>
       </c>
       <c r="HA6" s="1">
-        <v>0.08860759437084198</v>
+        <v>8.860759437084198E-2</v>
       </c>
       <c r="HB6" s="1">
         <v>3</v>
@@ -7394,10 +7741,10 @@
         <v>48</v>
       </c>
       <c r="HD6" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -7877,32 +8224,32 @@
         <v>944</v>
       </c>
       <c r="FS7" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU7" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="FV7" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="FW7" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="FX7" t="s">
         <v>48</v>
       </c>
       <c r="FY7" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="FZ7" s="1"/>
       <c r="GA7" s="1">
         <v>2024</v>
       </c>
       <c r="GB7" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="GC7" t="s">
         <v>941</v>
@@ -7965,7 +8312,7 @@
         <v>2.065000057220459</v>
       </c>
       <c r="GW7" s="1">
-        <v>0.059000000357627869</v>
+        <v>5.9000000357627869E-2</v>
       </c>
       <c r="GX7" s="1">
         <v>21.599031448364258</v>
@@ -7977,7 +8324,7 @@
         <v>9</v>
       </c>
       <c r="HA7" s="1">
-        <v>0.058064516633749008</v>
+        <v>5.8064516633749008E-2</v>
       </c>
       <c r="HB7" s="1">
         <v>3</v>
@@ -7986,10 +8333,10 @@
         <v>48</v>
       </c>
       <c r="HD7" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -8487,13 +8834,13 @@
         <v>945</v>
       </c>
       <c r="FS8" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="FU8" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="FV8" t="s">
         <v>1</v>
@@ -8505,14 +8852,14 @@
         <v>51</v>
       </c>
       <c r="FY8" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="FZ8" s="1"/>
       <c r="GA8" s="1">
         <v>2025</v>
       </c>
       <c r="GB8" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="GC8" t="s">
         <v>941</v>
@@ -8551,7 +8898,7 @@
         <v>39</v>
       </c>
       <c r="GO8" s="1">
-        <v>0.83600002527236939</v>
+        <v>0.83600002527236938</v>
       </c>
       <c r="GP8" s="1">
         <v>0.69499999284744263</v>
@@ -8575,10 +8922,10 @@
         <v>1.6469999551773071</v>
       </c>
       <c r="GW8" s="1">
-        <v>0.039000000804662705</v>
+        <v>3.9000000804662704E-2</v>
       </c>
       <c r="GX8" s="1">
-        <v>23.124273300170899</v>
+        <v>23.124273300170898</v>
       </c>
       <c r="GY8" s="1">
         <v>0</v>
@@ -8596,10 +8943,10 @@
         <v>50</v>
       </c>
       <c r="HD8" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -8915,13 +9262,13 @@
         <v>945</v>
       </c>
       <c r="FS9" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT9" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="FU9" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="FV9" t="s">
         <v>1</v>
@@ -8933,14 +9280,14 @@
         <v>51</v>
       </c>
       <c r="FY9" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="FZ9" s="1"/>
       <c r="GA9" s="1">
         <v>2024</v>
       </c>
       <c r="GB9" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="GC9" t="s">
         <v>941</v>
@@ -9003,7 +9350,7 @@
         <v>1.7430000305175781</v>
       </c>
       <c r="GW9" s="1">
-        <v>0.018999999389052391</v>
+        <v>1.8999999389052391E-2</v>
       </c>
       <c r="GX9" s="1">
         <v>16.573581695556641</v>
@@ -9024,10 +9371,10 @@
         <v>50</v>
       </c>
       <c r="HD9" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -9373,32 +9720,32 @@
         <v>944</v>
       </c>
       <c r="FS10" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT10" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="FU10" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="FV10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="FW10" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="FX10" t="s">
         <v>52</v>
       </c>
       <c r="FY10" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="FZ10" s="1"/>
       <c r="GA10" s="1">
         <v>2025</v>
       </c>
       <c r="GB10" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="GC10" t="s">
         <v>941</v>
@@ -9473,7 +9820,7 @@
         <v>4</v>
       </c>
       <c r="HA10" s="1">
-        <v>0.031496062874794006</v>
+        <v>3.1496062874794006E-2</v>
       </c>
       <c r="HB10" s="1">
         <v>2</v>
@@ -9482,10 +9829,10 @@
         <v>52</v>
       </c>
       <c r="HD10" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -9965,32 +10312,32 @@
         <v>944</v>
       </c>
       <c r="FS11" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT11" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="FU11" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="FV11" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="FW11" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="FX11" t="s">
         <v>52</v>
       </c>
       <c r="FY11" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="FZ11" s="1"/>
       <c r="GA11" s="1">
         <v>2024</v>
       </c>
       <c r="GB11" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="GC11" t="s">
         <v>941</v>
@@ -10032,7 +10379,7 @@
         <v>0.62699997425079346</v>
       </c>
       <c r="GP11" s="1">
-        <v>1.0670000314712525</v>
+        <v>1.0670000314712524</v>
       </c>
       <c r="GQ11" s="1">
         <v>0.75800001621246338</v>
@@ -10065,7 +10412,7 @@
         <v>2</v>
       </c>
       <c r="HA11" s="1">
-        <v>0.016000000759959221</v>
+        <v>1.6000000759959221E-2</v>
       </c>
       <c r="HB11" s="1">
         <v>2</v>
@@ -10074,10 +10421,10 @@
         <v>52</v>
       </c>
       <c r="HD11" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -10499,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="EY12" s="1">
-        <v>0.072882004082202911</v>
+        <v>7.2882004082202911E-2</v>
       </c>
       <c r="EZ12" t="s">
         <v>524</v>
@@ -10557,32 +10904,32 @@
         <v>944</v>
       </c>
       <c r="FS12" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT12" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="FU12" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="FV12" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="FW12" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="FX12" t="s">
         <v>53</v>
       </c>
       <c r="FY12" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="FZ12" s="1"/>
       <c r="GA12" s="1">
         <v>2024</v>
       </c>
       <c r="GB12" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="GC12" t="s">
         <v>941</v>
@@ -10624,13 +10971,13 @@
         <v>0.43000000715255737</v>
       </c>
       <c r="GP12" s="1">
-        <v>0.43799999356269837</v>
+        <v>0.43799999356269836</v>
       </c>
       <c r="GQ12" s="1">
         <v>0.37200000882148743</v>
       </c>
       <c r="GR12" s="1">
-        <v>0.090999998152256012</v>
+        <v>9.0999998152256012E-2</v>
       </c>
       <c r="GS12" s="1">
         <v>241.25399780273438</v>
@@ -10645,7 +10992,7 @@
         <v>1.5110000371932983</v>
       </c>
       <c r="GW12" s="1">
-        <v>0.082999996840953827</v>
+        <v>8.2999996840953827E-2</v>
       </c>
       <c r="GX12" s="1">
         <v>27.199850082397461</v>
@@ -10666,10 +11013,10 @@
         <v>53</v>
       </c>
       <c r="HD12" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -10937,7 +11284,7 @@
         <v>2</v>
       </c>
       <c r="EY13" s="1">
-        <v>0.073109261691570282</v>
+        <v>7.3109261691570282E-2</v>
       </c>
       <c r="EZ13" t="s">
         <v>524</v>
@@ -10995,32 +11342,32 @@
         <v>944</v>
       </c>
       <c r="FS13" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT13" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="FU13" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="FV13" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="FW13" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="FX13" t="s">
         <v>53</v>
       </c>
       <c r="FY13" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="FZ13" s="1"/>
       <c r="GA13" s="1">
         <v>2025</v>
       </c>
       <c r="GB13" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="GC13" t="s">
         <v>941</v>
@@ -11068,7 +11415,7 @@
         <v>0.34999999403953552</v>
       </c>
       <c r="GR13" s="1">
-        <v>0.086000002920627594</v>
+        <v>8.6000002920627594E-2</v>
       </c>
       <c r="GS13" s="1">
         <v>233.5</v>
@@ -11104,10 +11451,10 @@
         <v>53</v>
       </c>
       <c r="HD13" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -11433,32 +11780,32 @@
         <v>944</v>
       </c>
       <c r="FS14" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT14" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="FU14" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="FV14" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="FW14" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="FX14" t="s">
         <v>54</v>
       </c>
       <c r="FY14" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="FZ14" s="1"/>
       <c r="GA14" s="1">
         <v>2025</v>
       </c>
       <c r="GB14" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="GC14" t="s">
         <v>941</v>
@@ -11500,13 +11847,13 @@
         <v>0.59500002861022949</v>
       </c>
       <c r="GP14" s="1">
-        <v>0.60399997234344483</v>
+        <v>0.60399997234344482</v>
       </c>
       <c r="GQ14" s="1">
-        <v>0.546999990940094</v>
+        <v>0.54699999094009399</v>
       </c>
       <c r="GR14" s="1">
-        <v>0.093000002205371857</v>
+        <v>9.3000002205371857E-2</v>
       </c>
       <c r="GS14" s="1">
         <v>330.79098510742188</v>
@@ -11521,7 +11868,7 @@
         <v>1.2009999752044678</v>
       </c>
       <c r="GW14" s="1">
-        <v>0.056000001728534699</v>
+        <v>5.6000001728534698E-2</v>
       </c>
       <c r="GX14" s="1">
         <v>17.457632064819336</v>
@@ -11542,10 +11889,10 @@
         <v>54</v>
       </c>
       <c r="HD14" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -12025,32 +12372,32 @@
         <v>944</v>
       </c>
       <c r="FS15" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT15" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="FU15" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="FV15" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="FW15" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="FX15" t="s">
         <v>54</v>
       </c>
       <c r="FY15" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="FZ15" s="1"/>
       <c r="GA15" s="1">
         <v>2024</v>
       </c>
       <c r="GB15" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="GC15" t="s">
         <v>941</v>
@@ -12098,7 +12445,7 @@
         <v>0.57499998807907104</v>
       </c>
       <c r="GR15" s="1">
-        <v>0.098999999463558197</v>
+        <v>9.8999999463558197E-2</v>
       </c>
       <c r="GS15" s="1">
         <v>354.56298828125</v>
@@ -12113,7 +12460,7 @@
         <v>1.1030000448226929</v>
       </c>
       <c r="GW15" s="1">
-        <v>0.028000000864267349</v>
+        <v>2.8000000864267349E-2</v>
       </c>
       <c r="GX15" s="1">
         <v>18.260940551757813</v>
@@ -12134,10 +12481,10 @@
         <v>54</v>
       </c>
       <c r="HD15" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -12581,10 +12928,10 @@
         <v>1</v>
       </c>
       <c r="FS16" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT16" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="FU16" t="s">
         <v>1</v>
@@ -12638,10 +12985,10 @@
         <v>55</v>
       </c>
       <c r="HD16" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -12931,10 +13278,10 @@
         <v>1</v>
       </c>
       <c r="FS17" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="FU17" t="s">
         <v>1</v>
@@ -12988,10 +13335,10 @@
         <v>55</v>
       </c>
       <c r="HD17" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -13471,32 +13818,32 @@
         <v>944</v>
       </c>
       <c r="FS18" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT18" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="FU18" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="FV18" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="FW18" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="FX18" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="FY18" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="FZ18" s="1"/>
       <c r="GA18" s="1">
         <v>2024</v>
       </c>
       <c r="GB18" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="GC18" t="s">
         <v>941</v>
@@ -13538,7 +13885,7 @@
         <v>0.82099997997283936</v>
       </c>
       <c r="GP18" s="1">
-        <v>0.82899999618530274</v>
+        <v>0.82899999618530273</v>
       </c>
       <c r="GQ18" s="1">
         <v>0.62000000476837158</v>
@@ -13553,7 +13900,7 @@
         <v>61.077999114990234</v>
       </c>
       <c r="GU18" s="1">
-        <v>16.468999862670899</v>
+        <v>16.468999862670898</v>
       </c>
       <c r="GV18" s="1">
         <v>1.8270000219345093</v>
@@ -13571,7 +13918,7 @@
         <v>4</v>
       </c>
       <c r="HA18" s="1">
-        <v>0.038834951817989349</v>
+        <v>3.8834951817989349E-2</v>
       </c>
       <c r="HB18" s="1">
         <v>2</v>
@@ -13580,10 +13927,10 @@
         <v>57</v>
       </c>
       <c r="HD18" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -13909,32 +14256,32 @@
         <v>944</v>
       </c>
       <c r="FS19" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT19" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="FU19" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="FV19" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="FW19" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="FX19" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="FY19" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="FZ19" s="1"/>
       <c r="GA19" s="1">
         <v>2025</v>
       </c>
       <c r="GB19" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="GC19" t="s">
         <v>941</v>
@@ -14018,10 +14365,10 @@
         <v>57</v>
       </c>
       <c r="HD19" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -14347,32 +14694,32 @@
         <v>944</v>
       </c>
       <c r="FS20" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="FU20" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="FV20" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="FW20" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="FX20" t="s">
         <v>59</v>
       </c>
       <c r="FY20" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="FZ20" s="1"/>
       <c r="GA20" s="1">
         <v>2025</v>
       </c>
       <c r="GB20" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="GC20" t="s">
         <v>941</v>
@@ -14411,7 +14758,7 @@
         <v>60</v>
       </c>
       <c r="GO20" s="1">
-        <v>0.34499999880790711</v>
+        <v>0.3449999988079071</v>
       </c>
       <c r="GP20" s="1">
         <v>0.25699999928474426</v>
@@ -14420,7 +14767,7 @@
         <v>0.28600001335144043</v>
       </c>
       <c r="GR20" s="1">
-        <v>0.065999999642372131</v>
+        <v>6.5999999642372131E-2</v>
       </c>
       <c r="GS20" s="1">
         <v>204.66700744628906</v>
@@ -14435,7 +14782,7 @@
         <v>0.91699999570846558</v>
       </c>
       <c r="GW20" s="1">
-        <v>0.059999998658895493</v>
+        <v>5.9999998658895493E-2</v>
       </c>
       <c r="GX20" s="1">
         <v>29.625</v>
@@ -14456,10 +14803,10 @@
         <v>58</v>
       </c>
       <c r="HD20" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -14939,32 +15286,32 @@
         <v>944</v>
       </c>
       <c r="FS21" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT21" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="FU21" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="FV21" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="FW21" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="FX21" t="s">
         <v>59</v>
       </c>
       <c r="FY21" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="FZ21" s="1"/>
       <c r="GA21" s="1">
         <v>2024</v>
       </c>
       <c r="GB21" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="GC21" t="s">
         <v>941</v>
@@ -15012,7 +15359,7 @@
         <v>0.31700000166893005</v>
       </c>
       <c r="GR21" s="1">
-        <v>0.070000000298023224</v>
+        <v>7.0000000298023224E-2</v>
       </c>
       <c r="GS21" s="1">
         <v>242.16200256347656</v>
@@ -15027,7 +15374,7 @@
         <v>0.72000002861022949</v>
       </c>
       <c r="GW21" s="1">
-        <v>0.083999998867511749</v>
+        <v>8.3999998867511749E-2</v>
       </c>
       <c r="GX21" s="1">
         <v>27.04692268371582</v>
@@ -15039,7 +15386,7 @@
         <v>3</v>
       </c>
       <c r="HA21" s="1">
-        <v>0.046153847128152847</v>
+        <v>4.6153847128152847E-2</v>
       </c>
       <c r="HB21" s="1">
         <v>1</v>
@@ -15048,10 +15395,10 @@
         <v>58</v>
       </c>
       <c r="HD21" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -15341,10 +15688,10 @@
         <v>1</v>
       </c>
       <c r="FS22" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT22" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="FU22" t="s">
         <v>1</v>
@@ -15398,10 +15745,10 @@
         <v>60</v>
       </c>
       <c r="HD22" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -15681,10 +16028,10 @@
         <v>1</v>
       </c>
       <c r="FS23" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT23" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="FU23" t="s">
         <v>1</v>
@@ -15738,10 +16085,10 @@
         <v>60</v>
       </c>
       <c r="HD23" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1</v>
       </c>
@@ -16197,32 +16544,32 @@
         <v>944</v>
       </c>
       <c r="FS24" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT24" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="FU24" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="FV24" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="FW24" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="FX24" t="s">
         <v>62</v>
       </c>
       <c r="FY24" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="FZ24" s="1"/>
       <c r="GA24" s="1">
         <v>2024</v>
       </c>
       <c r="GB24" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="GC24" t="s">
         <v>941</v>
@@ -16264,7 +16611,7 @@
         <v>1.0479999780654907</v>
       </c>
       <c r="GP24" s="1">
-        <v>1.2339999675750733</v>
+        <v>1.2339999675750732</v>
       </c>
       <c r="GQ24" s="1">
         <v>0.98199999332427979</v>
@@ -16285,7 +16632,7 @@
         <v>2.7179999351501465</v>
       </c>
       <c r="GW24" s="1">
-        <v>0.063000001013278961</v>
+        <v>6.3000001013278961E-2</v>
       </c>
       <c r="GX24" s="1">
         <v>22.270563125610352</v>
@@ -16297,7 +16644,7 @@
         <v>6</v>
       </c>
       <c r="HA24" s="1">
-        <v>0.01875000074505806</v>
+        <v>1.875000074505806E-2</v>
       </c>
       <c r="HB24" s="1">
         <v>3</v>
@@ -16306,10 +16653,10 @@
         <v>62</v>
       </c>
       <c r="HD24" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -16635,32 +16982,32 @@
         <v>944</v>
       </c>
       <c r="FS25" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT25" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="FU25" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="FV25" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="FW25" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="FX25" t="s">
         <v>62</v>
       </c>
       <c r="FY25" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="FZ25" s="1"/>
       <c r="GA25" s="1">
         <v>2025</v>
       </c>
       <c r="GB25" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="GC25" t="s">
         <v>941</v>
@@ -16702,7 +17049,7 @@
         <v>0.87599998712539673</v>
       </c>
       <c r="GP25" s="1">
-        <v>0.83600002527236939</v>
+        <v>0.83600002527236938</v>
       </c>
       <c r="GQ25" s="1">
         <v>0.70200002193450928</v>
@@ -16744,10 +17091,10 @@
         <v>62</v>
       </c>
       <c r="HD25" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -17169,7 +17516,7 @@
         <v>0</v>
       </c>
       <c r="EY26" s="1">
-        <v>0.044253610074520111</v>
+        <v>4.4253610074520111E-2</v>
       </c>
       <c r="EZ26" t="s">
         <v>524</v>
@@ -17227,32 +17574,32 @@
         <v>944</v>
       </c>
       <c r="FS26" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT26" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU26" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="FV26" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="FW26" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="FX26" t="s">
         <v>63</v>
       </c>
       <c r="FY26" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="FZ26" s="1"/>
       <c r="GA26" s="1">
         <v>2024</v>
       </c>
       <c r="GB26" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="GC26" t="s">
         <v>941</v>
@@ -17315,7 +17662,7 @@
         <v>1.7580000162124634</v>
       </c>
       <c r="GW26" s="1">
-        <v>0.016000000759959221</v>
+        <v>1.6000000759959221E-2</v>
       </c>
       <c r="GX26" s="1">
         <v>21.208963394165039</v>
@@ -17327,7 +17674,7 @@
         <v>6</v>
       </c>
       <c r="HA26" s="1">
-        <v>0.031088082119822502</v>
+        <v>3.1088082119822502E-2</v>
       </c>
       <c r="HB26" s="1">
         <v>3</v>
@@ -17336,10 +17683,10 @@
         <v>63</v>
       </c>
       <c r="HD26" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -17607,7 +17954,7 @@
         <v>0</v>
       </c>
       <c r="EY27" s="1">
-        <v>0.045674171298742294</v>
+        <v>4.5674171298742294E-2</v>
       </c>
       <c r="EZ27" t="s">
         <v>524</v>
@@ -17665,32 +18012,32 @@
         <v>944</v>
       </c>
       <c r="FS27" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT27" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU27" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="FV27" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="FW27" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="FX27" t="s">
         <v>63</v>
       </c>
       <c r="FY27" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="FZ27" s="1"/>
       <c r="GA27" s="1">
         <v>2025</v>
       </c>
       <c r="GB27" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="GC27" t="s">
         <v>941</v>
@@ -17753,7 +18100,7 @@
         <v>1.8059999942779541</v>
       </c>
       <c r="GW27" s="1">
-        <v>0.087999999523162842</v>
+        <v>8.7999999523162842E-2</v>
       </c>
       <c r="GX27" s="1">
         <v>19.366771697998047</v>
@@ -17765,7 +18112,7 @@
         <v>11</v>
       </c>
       <c r="HA27" s="1">
-        <v>0.057291667908430099</v>
+        <v>5.7291667908430099E-2</v>
       </c>
       <c r="HB27" s="1">
         <v>3</v>
@@ -17774,10 +18121,10 @@
         <v>63</v>
       </c>
       <c r="HD27" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -18103,32 +18450,32 @@
         <v>944</v>
       </c>
       <c r="FS28" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT28" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="FU28" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="FV28" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="FW28" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="FX28" t="s">
         <v>64</v>
       </c>
       <c r="FY28" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="FZ28" s="1"/>
       <c r="GA28" s="1">
         <v>2025</v>
       </c>
       <c r="GB28" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="GC28" t="s">
         <v>941</v>
@@ -18176,7 +18523,7 @@
         <v>0.64499998092651367</v>
       </c>
       <c r="GR28" s="1">
-        <v>0.23600000143051148</v>
+        <v>0.23600000143051147</v>
       </c>
       <c r="GS28" s="1">
         <v>582.25897216796875</v>
@@ -18185,13 +18532,13 @@
         <v>92.527999877929688</v>
       </c>
       <c r="GU28" s="1">
-        <v>21.801000595092774</v>
+        <v>21.801000595092773</v>
       </c>
       <c r="GV28" s="1">
         <v>2.9040000438690186</v>
       </c>
       <c r="GW28" s="1">
-        <v>0.096000000834465027</v>
+        <v>9.6000000834465027E-2</v>
       </c>
       <c r="GX28" s="1">
         <v>24.657241821289063</v>
@@ -18203,7 +18550,7 @@
         <v>8</v>
       </c>
       <c r="HA28" s="1">
-        <v>0.045977011322975159</v>
+        <v>4.5977011322975159E-2</v>
       </c>
       <c r="HB28" s="1">
         <v>2</v>
@@ -18212,10 +18559,10 @@
         <v>64</v>
       </c>
       <c r="HD28" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -18695,32 +19042,32 @@
         <v>944</v>
       </c>
       <c r="FS29" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT29" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="FU29" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="FV29" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="FW29" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="FX29" t="s">
         <v>64</v>
       </c>
       <c r="FY29" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="FZ29" s="1"/>
       <c r="GA29" s="1">
         <v>2024</v>
       </c>
       <c r="GB29" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="GC29" t="s">
         <v>941</v>
@@ -18777,13 +19124,13 @@
         <v>88.282997131347656</v>
       </c>
       <c r="GU29" s="1">
-        <v>20.843999862670899</v>
+        <v>20.843999862670898</v>
       </c>
       <c r="GV29" s="1">
         <v>3.6919999122619629</v>
       </c>
       <c r="GW29" s="1">
-        <v>0.082000002264976501</v>
+        <v>8.2000002264976501E-2</v>
       </c>
       <c r="GX29" s="1">
         <v>21.82325553894043</v>
@@ -18795,7 +19142,7 @@
         <v>6</v>
       </c>
       <c r="HA29" s="1">
-        <v>0.03488372266292572</v>
+        <v>3.488372266292572E-2</v>
       </c>
       <c r="HB29" s="1">
         <v>2</v>
@@ -18804,10 +19151,10 @@
         <v>64</v>
       </c>
       <c r="HD29" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -19229,7 +19576,7 @@
         <v>0</v>
       </c>
       <c r="EY30" s="1">
-        <v>0.00035429286072030663</v>
+        <v>3.5429286072030663E-4</v>
       </c>
       <c r="EZ30" t="s">
         <v>524</v>
@@ -19287,19 +19634,19 @@
         <v>944</v>
       </c>
       <c r="FS30" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT30" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU30" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="FV30" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="FW30" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="FX30" t="s">
         <v>65</v>
@@ -19312,7 +19659,7 @@
         <v>2024</v>
       </c>
       <c r="GB30" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="GC30" t="s">
         <v>941</v>
@@ -19360,7 +19707,7 @@
         <v>0.42699998617172241</v>
       </c>
       <c r="GR30" s="1">
-        <v>0.086000002920627594</v>
+        <v>8.6000002920627594E-2</v>
       </c>
       <c r="GS30" s="1">
         <v>282.76199340820313</v>
@@ -19375,7 +19722,7 @@
         <v>1.0759999752044678</v>
       </c>
       <c r="GW30" s="1">
-        <v>0.05299999937415123</v>
+        <v>5.299999937415123E-2</v>
       </c>
       <c r="GX30" s="1">
         <v>37.175571441650391</v>
@@ -19387,7 +19734,7 @@
         <v>3</v>
       </c>
       <c r="HA30" s="1">
-        <v>0.049180328845977783</v>
+        <v>4.9180328845977783E-2</v>
       </c>
       <c r="HB30" s="1">
         <v>1</v>
@@ -19396,10 +19743,10 @@
         <v>65</v>
       </c>
       <c r="HD30" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -19725,19 +20072,19 @@
         <v>944</v>
       </c>
       <c r="FS31" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT31" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU31" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="FV31" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="FW31" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="FX31" t="s">
         <v>65</v>
@@ -19750,7 +20097,7 @@
         <v>2025</v>
       </c>
       <c r="GB31" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="GC31" t="s">
         <v>941</v>
@@ -19789,7 +20136,7 @@
         <v>75</v>
       </c>
       <c r="GO31" s="1">
-        <v>0.43399998545646668</v>
+        <v>0.43399998545646667</v>
       </c>
       <c r="GP31" s="1">
         <v>0.53100001811981201</v>
@@ -19798,7 +20145,7 @@
         <v>0.49200001358985901</v>
       </c>
       <c r="GR31" s="1">
-        <v>0.094999998807907105</v>
+        <v>9.4999998807907104E-2</v>
       </c>
       <c r="GS31" s="1">
         <v>352.197998046875</v>
@@ -19813,7 +20160,7 @@
         <v>1.1929999589920044</v>
       </c>
       <c r="GW31" s="1">
-        <v>0.075000002980232239</v>
+        <v>7.5000002980232239E-2</v>
       </c>
       <c r="GX31" s="1">
         <v>39.285606384277344</v>
@@ -19834,10 +20181,10 @@
         <v>65</v>
       </c>
       <c r="HD31" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1</v>
       </c>
@@ -20317,19 +20664,19 @@
         <v>944</v>
       </c>
       <c r="FS32" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT32" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU32" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="FV32" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="FW32" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="FX32" t="s">
         <v>66</v>
@@ -20342,7 +20689,7 @@
         <v>2024</v>
       </c>
       <c r="GB32" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="GC32" t="s">
         <v>941</v>
@@ -20390,7 +20737,7 @@
         <v>0.37999999523162842</v>
       </c>
       <c r="GR32" s="1">
-        <v>0.068999998271465302</v>
+        <v>6.8999998271465302E-2</v>
       </c>
       <c r="GS32" s="1">
         <v>304.3330078125</v>
@@ -20405,7 +20752,7 @@
         <v>2.3810000419616699</v>
       </c>
       <c r="GW32" s="1">
-        <v>0.075999997556209564</v>
+        <v>7.5999997556209564E-2</v>
       </c>
       <c r="GX32" s="1">
         <v>23.267875671386719</v>
@@ -20417,7 +20764,7 @@
         <v>1</v>
       </c>
       <c r="HA32" s="1">
-        <v>0.008849557489156723</v>
+        <v>8.849557489156723E-3</v>
       </c>
       <c r="HB32" s="1">
         <v>1</v>
@@ -20426,10 +20773,10 @@
         <v>66</v>
       </c>
       <c r="HD32" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -20755,19 +21102,19 @@
         <v>944</v>
       </c>
       <c r="FS33" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT33" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU33" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="FV33" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="FW33" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="FX33" t="s">
         <v>66</v>
@@ -20780,7 +21127,7 @@
         <v>2025</v>
       </c>
       <c r="GB33" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="GC33" t="s">
         <v>941</v>
@@ -20828,7 +21175,7 @@
         <v>0.32899999618530273</v>
       </c>
       <c r="GR33" s="1">
-        <v>0.068000003695487976</v>
+        <v>6.8000003695487976E-2</v>
       </c>
       <c r="GS33" s="1">
         <v>266.86300659179688</v>
@@ -20840,10 +21187,10 @@
         <v>11.369000434875488</v>
       </c>
       <c r="GV33" s="1">
-        <v>2.0550000667572022</v>
+        <v>2.0550000667572021</v>
       </c>
       <c r="GW33" s="1">
-        <v>0.05299999937415123</v>
+        <v>5.299999937415123E-2</v>
       </c>
       <c r="GX33" s="1">
         <v>23.600429534912109</v>
@@ -20855,7 +21202,7 @@
         <v>1</v>
       </c>
       <c r="HA33" s="1">
-        <v>0.01075268816202879</v>
+        <v>1.075268816202879E-2</v>
       </c>
       <c r="HB33" s="1">
         <v>1</v>
@@ -20864,10 +21211,10 @@
         <v>66</v>
       </c>
       <c r="HD33" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -21193,32 +21540,32 @@
         <v>944</v>
       </c>
       <c r="FS34" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT34" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU34" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="FV34" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="FW34" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="FX34" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="FY34" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="FZ34" s="1"/>
       <c r="GA34" s="1">
         <v>2025</v>
       </c>
       <c r="GB34" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="GC34" t="s">
         <v>941</v>
@@ -21257,7 +21604,7 @@
         <v>26</v>
       </c>
       <c r="GO34" s="1">
-        <v>0.546999990940094</v>
+        <v>0.54699999094009399</v>
       </c>
       <c r="GP34" s="1">
         <v>0.56400001049041748</v>
@@ -21281,7 +21628,7 @@
         <v>1.5440000295639038</v>
       </c>
       <c r="GW34" s="1">
-        <v>0.026000000536441803</v>
+        <v>2.6000000536441803E-2</v>
       </c>
       <c r="GX34" s="1">
         <v>22.868051528930664</v>
@@ -21302,10 +21649,10 @@
         <v>67</v>
       </c>
       <c r="HD34" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -21785,32 +22132,32 @@
         <v>944</v>
       </c>
       <c r="FS35" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT35" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU35" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="FV35" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="FW35" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="FX35" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="FY35" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="FZ35" s="1"/>
       <c r="GA35" s="1">
         <v>2024</v>
       </c>
       <c r="GB35" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="GC35" t="s">
         <v>941</v>
@@ -21873,7 +22220,7 @@
         <v>1.5130000114440918</v>
       </c>
       <c r="GW35" s="1">
-        <v>0.037999998778104782</v>
+        <v>3.7999998778104782E-2</v>
       </c>
       <c r="GX35" s="1">
         <v>29.260068893432617</v>
@@ -21894,10 +22241,10 @@
         <v>67</v>
       </c>
       <c r="HD35" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1</v>
       </c>
@@ -22319,7 +22666,7 @@
         <v>0</v>
       </c>
       <c r="EY36" s="1">
-        <v>0.00093396683223545551</v>
+        <v>9.3396683223545551E-4</v>
       </c>
       <c r="EZ36" t="s">
         <v>524</v>
@@ -22377,19 +22724,19 @@
         <v>944</v>
       </c>
       <c r="FS36" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT36" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="FU36" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="FV36" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="FW36" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="FX36" t="s">
         <v>69</v>
@@ -22402,7 +22749,7 @@
         <v>2024</v>
       </c>
       <c r="GB36" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="GC36" t="s">
         <v>941</v>
@@ -22486,10 +22833,10 @@
         <v>69</v>
       </c>
       <c r="HD36" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -22757,7 +23104,7 @@
         <v>0</v>
       </c>
       <c r="EY37" s="1">
-        <v>0.0009377304813824594</v>
+        <v>9.377304813824594E-4</v>
       </c>
       <c r="EZ37" t="s">
         <v>524</v>
@@ -22815,19 +23162,19 @@
         <v>944</v>
       </c>
       <c r="FS37" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT37" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="FU37" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="FV37" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="FW37" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="FX37" t="s">
         <v>69</v>
@@ -22840,7 +23187,7 @@
         <v>2025</v>
       </c>
       <c r="GB37" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="GC37" t="s">
         <v>941</v>
@@ -22885,7 +23232,7 @@
         <v>0.59200000762939453</v>
       </c>
       <c r="GQ37" s="1">
-        <v>0.36500000953674317</v>
+        <v>0.36500000953674316</v>
       </c>
       <c r="GR37" s="1">
         <v>0.25200000405311584</v>
@@ -22924,10 +23271,10 @@
         <v>69</v>
       </c>
       <c r="HD37" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1</v>
       </c>
@@ -23239,19 +23586,19 @@
         <v>944</v>
       </c>
       <c r="FS38" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT38" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU38" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="FV38" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="FW38" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="FX38" t="s">
         <v>70</v>
@@ -23264,7 +23611,7 @@
         <v>2024</v>
       </c>
       <c r="GB38" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="GC38" t="s">
         <v>941</v>
@@ -23327,7 +23674,7 @@
         <v>2.684999942779541</v>
       </c>
       <c r="GW38" s="1">
-        <v>0.071000002324581146</v>
+        <v>7.1000002324581146E-2</v>
       </c>
       <c r="GX38" s="1">
         <v>20.418458938598633</v>
@@ -23339,7 +23686,7 @@
         <v>21</v>
       </c>
       <c r="HA38" s="1">
-        <v>0.087499998509883881</v>
+        <v>8.7499998509883881E-2</v>
       </c>
       <c r="HB38" s="1">
         <v>3</v>
@@ -23348,10 +23695,10 @@
         <v>70</v>
       </c>
       <c r="HD38" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -23677,19 +24024,19 @@
         <v>944</v>
       </c>
       <c r="FS39" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT39" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU39" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="FV39" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="FW39" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="FX39" t="s">
         <v>70</v>
@@ -23702,7 +24049,7 @@
         <v>2025</v>
       </c>
       <c r="GB39" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="GC39" t="s">
         <v>941</v>
@@ -23765,7 +24112,7 @@
         <v>2.6830000877380371</v>
       </c>
       <c r="GW39" s="1">
-        <v>0.087999999523162842</v>
+        <v>8.7999999523162842E-2</v>
       </c>
       <c r="GX39" s="1">
         <v>21.938272476196289</v>
@@ -23786,10 +24133,10 @@
         <v>70</v>
       </c>
       <c r="HD39" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1</v>
       </c>
@@ -24115,16 +24462,16 @@
         <v>946</v>
       </c>
       <c r="FS40" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT40" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU40" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="FV40" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="FW40" t="s">
         <v>1</v>
@@ -24140,7 +24487,7 @@
         <v>2025</v>
       </c>
       <c r="GB40" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="GC40" t="s">
         <v>941</v>
@@ -24185,7 +24532,7 @@
         <v>0.63899999856948853</v>
       </c>
       <c r="GQ40" s="1">
-        <v>0.67900002002716065</v>
+        <v>0.67900002002716064</v>
       </c>
       <c r="GR40" s="1">
         <v>0.17499999701976776</v>
@@ -24203,7 +24550,7 @@
         <v>1.2890000343322754</v>
       </c>
       <c r="GW40" s="1">
-        <v>0.026000000536441803</v>
+        <v>2.6000000536441803E-2</v>
       </c>
       <c r="GX40" s="1">
         <v>27.146852493286133</v>
@@ -24224,10 +24571,10 @@
         <v>71</v>
       </c>
       <c r="HD40" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1</v>
       </c>
@@ -24707,16 +25054,16 @@
         <v>946</v>
       </c>
       <c r="FS41" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT41" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU41" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="FV41" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="FW41" t="s">
         <v>1</v>
@@ -24732,7 +25079,7 @@
         <v>2024</v>
       </c>
       <c r="GB41" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="GC41" t="s">
         <v>941</v>
@@ -24792,10 +25139,10 @@
         <v>11.279999732971191</v>
       </c>
       <c r="GV41" s="1">
-        <v>1.1649999618530274</v>
+        <v>1.1649999618530273</v>
       </c>
       <c r="GW41" s="1">
-        <v>0.027000000700354576</v>
+        <v>2.7000000700354576E-2</v>
       </c>
       <c r="GX41" s="1">
         <v>27.920000076293945</v>
@@ -24816,10 +25163,10 @@
         <v>71</v>
       </c>
       <c r="HD41" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1</v>
       </c>
@@ -25299,32 +25646,32 @@
         <v>944</v>
       </c>
       <c r="FS42" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT42" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU42" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="FV42" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="FW42" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="FX42" t="s">
         <v>74</v>
       </c>
       <c r="FY42" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="FZ42" s="1"/>
       <c r="GA42" s="1">
         <v>2024</v>
       </c>
       <c r="GB42" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="GC42" t="s">
         <v>941</v>
@@ -25408,10 +25755,10 @@
         <v>74</v>
       </c>
       <c r="HD42" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -25909,32 +26256,32 @@
         <v>944</v>
       </c>
       <c r="FS43" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT43" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU43" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="FV43" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="FW43" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="FX43" t="s">
         <v>74</v>
       </c>
       <c r="FY43" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="FZ43" s="1"/>
       <c r="GA43" s="1">
         <v>2025</v>
       </c>
       <c r="GB43" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="GC43" t="s">
         <v>941</v>
@@ -26009,7 +26356,7 @@
         <v>3</v>
       </c>
       <c r="HA43" s="1">
-        <v>0.025862069800496101</v>
+        <v>2.5862069800496101E-2</v>
       </c>
       <c r="HB43" s="1">
         <v>3</v>
@@ -26018,10 +26365,10 @@
         <v>74</v>
       </c>
       <c r="HD43" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1</v>
       </c>
@@ -26501,32 +26848,32 @@
         <v>944</v>
       </c>
       <c r="FS44" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT44" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU44" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="FV44" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="FW44" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="FX44" t="s">
         <v>75</v>
       </c>
       <c r="FY44" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="FZ44" s="1"/>
       <c r="GA44" s="1">
         <v>2024</v>
       </c>
       <c r="GB44" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="GC44" t="s">
         <v>941</v>
@@ -26589,7 +26936,7 @@
         <v>2.0429999828338623</v>
       </c>
       <c r="GW44" s="1">
-        <v>0.071000002324581146</v>
+        <v>7.1000002324581146E-2</v>
       </c>
       <c r="GX44" s="1">
         <v>33.471454620361328</v>
@@ -26601,7 +26948,7 @@
         <v>1</v>
       </c>
       <c r="HA44" s="1">
-        <v>0.0097087379544973374</v>
+        <v>9.7087379544973373E-3</v>
       </c>
       <c r="HB44" s="1">
         <v>2</v>
@@ -26610,10 +26957,10 @@
         <v>75</v>
       </c>
       <c r="HD44" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -26939,32 +27286,32 @@
         <v>944</v>
       </c>
       <c r="FS45" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT45" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU45" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="FV45" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="FW45" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="FX45" t="s">
         <v>75</v>
       </c>
       <c r="FY45" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="FZ45" s="1"/>
       <c r="GA45" s="1">
         <v>2025</v>
       </c>
       <c r="GB45" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="GC45" t="s">
         <v>941</v>
@@ -27027,7 +27374,7 @@
         <v>2.5899999141693115</v>
       </c>
       <c r="GW45" s="1">
-        <v>0.076999999582767487</v>
+        <v>7.6999999582767487E-2</v>
       </c>
       <c r="GX45" s="1">
         <v>32.292457580566406</v>
@@ -27039,7 +27386,7 @@
         <v>1</v>
       </c>
       <c r="HA45" s="1">
-        <v>0.0084745762869715691</v>
+        <v>8.4745762869715691E-3</v>
       </c>
       <c r="HB45" s="1">
         <v>2</v>
@@ -27048,10 +27395,10 @@
         <v>75</v>
       </c>
       <c r="HD45" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1</v>
       </c>
@@ -27531,32 +27878,32 @@
         <v>944</v>
       </c>
       <c r="FS46" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT46" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU46" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="FV46" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="FW46" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="FX46" t="s">
         <v>76</v>
       </c>
       <c r="FY46" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="FZ46" s="1"/>
       <c r="GA46" s="1">
         <v>2024</v>
       </c>
       <c r="GB46" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="GC46" t="s">
         <v>941</v>
@@ -27604,7 +27951,7 @@
         <v>0.49300000071525574</v>
       </c>
       <c r="GR46" s="1">
-        <v>0.075000002980232239</v>
+        <v>7.5000002980232239E-2</v>
       </c>
       <c r="GS46" s="1">
         <v>391.73699951171875</v>
@@ -27619,7 +27966,7 @@
         <v>1.6460000276565552</v>
       </c>
       <c r="GW46" s="1">
-        <v>0.014999999664723873</v>
+        <v>1.4999999664723873E-2</v>
       </c>
       <c r="GX46" s="1">
         <v>25.664175033569336</v>
@@ -27640,10 +27987,10 @@
         <v>76</v>
       </c>
       <c r="HD46" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -27969,32 +28316,32 @@
         <v>944</v>
       </c>
       <c r="FS47" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT47" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU47" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="FV47" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="FW47" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="FX47" t="s">
         <v>76</v>
       </c>
       <c r="FY47" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="FZ47" s="1"/>
       <c r="GA47" s="1">
         <v>2025</v>
       </c>
       <c r="GB47" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="GC47" t="s">
         <v>941</v>
@@ -28057,7 +28404,7 @@
         <v>2.3399999141693115</v>
       </c>
       <c r="GW47" s="1">
-        <v>0.046000000089406967</v>
+        <v>4.6000000089406967E-2</v>
       </c>
       <c r="GX47" s="1">
         <v>24.153924942016602</v>
@@ -28069,7 +28416,7 @@
         <v>1</v>
       </c>
       <c r="HA47" s="1">
-        <v>0.0074074072763323784</v>
+        <v>7.4074072763323784E-3</v>
       </c>
       <c r="HB47" s="1">
         <v>1</v>
@@ -28078,10 +28425,10 @@
         <v>76</v>
       </c>
       <c r="HD47" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1</v>
       </c>
@@ -28525,10 +28872,10 @@
         <v>1</v>
       </c>
       <c r="FS48" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT48" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="FU48" t="s">
         <v>1</v>
@@ -28582,10 +28929,10 @@
         <v>78</v>
       </c>
       <c r="HD48" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -28875,10 +29222,10 @@
         <v>1</v>
       </c>
       <c r="FS49" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT49" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="FU49" t="s">
         <v>1</v>
@@ -28932,10 +29279,10 @@
         <v>78</v>
       </c>
       <c r="HD49" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>10</v>
       </c>
@@ -29261,19 +29608,19 @@
         <v>944</v>
       </c>
       <c r="FS50" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT50" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU50" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="FV50" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="FW50" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="FX50" t="s">
         <v>79</v>
@@ -29286,7 +29633,7 @@
         <v>2025</v>
       </c>
       <c r="GB50" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="GC50" t="s">
         <v>941</v>
@@ -29349,7 +29696,7 @@
         <v>2.2330000400543213</v>
       </c>
       <c r="GW50" s="1">
-        <v>0.05000000074505806</v>
+        <v>5.000000074505806E-2</v>
       </c>
       <c r="GX50" s="1">
         <v>20.042236328125</v>
@@ -29361,7 +29708,7 @@
         <v>1</v>
       </c>
       <c r="HA50" s="1">
-        <v>0.01315789483487606</v>
+        <v>1.315789483487606E-2</v>
       </c>
       <c r="HB50" s="1">
         <v>1</v>
@@ -29370,10 +29717,10 @@
         <v>79</v>
       </c>
       <c r="HD50" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1</v>
       </c>
@@ -29853,19 +30200,19 @@
         <v>944</v>
       </c>
       <c r="FS51" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT51" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU51" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="FV51" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="FW51" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="FX51" t="s">
         <v>79</v>
@@ -29878,7 +30225,7 @@
         <v>2024</v>
       </c>
       <c r="GB51" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="GC51" t="s">
         <v>941</v>
@@ -29941,7 +30288,7 @@
         <v>2.124000072479248</v>
       </c>
       <c r="GW51" s="1">
-        <v>0.057000000029802322</v>
+        <v>5.7000000029802322E-2</v>
       </c>
       <c r="GX51" s="1">
         <v>21.796249389648438</v>
@@ -29962,10 +30309,10 @@
         <v>79</v>
       </c>
       <c r="HD51" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1</v>
       </c>
@@ -30387,7 +30734,7 @@
         <v>0</v>
       </c>
       <c r="EY52" s="1">
-        <v>1.084854006767273</v>
+        <v>1.0848540067672729</v>
       </c>
       <c r="EZ52" t="s">
         <v>524</v>
@@ -30445,10 +30792,10 @@
         <v>944</v>
       </c>
       <c r="FS52" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT52" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU52" t="s">
         <v>1</v>
@@ -30463,14 +30810,14 @@
         <v>81</v>
       </c>
       <c r="FY52" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="FZ52" s="1"/>
       <c r="GA52" s="1">
         <v>2024</v>
       </c>
       <c r="GB52" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="GC52" t="s">
         <v>941</v>
@@ -30509,7 +30856,7 @@
         <v>96</v>
       </c>
       <c r="GO52" s="1">
-        <v>1.3589999675750733</v>
+        <v>1.3589999675750732</v>
       </c>
       <c r="GP52" s="1">
         <v>1.781000018119812</v>
@@ -30518,7 +30865,7 @@
         <v>0.9179999828338623</v>
       </c>
       <c r="GR52" s="1">
-        <v>0.296999990940094</v>
+        <v>0.29699999094009399</v>
       </c>
       <c r="GS52" s="1">
         <v>696.8590087890625</v>
@@ -30533,7 +30880,7 @@
         <v>2.8329999446868896</v>
       </c>
       <c r="GW52" s="1">
-        <v>0.096000000834465027</v>
+        <v>9.6000000834465027E-2</v>
       </c>
       <c r="GX52" s="1">
         <v>21.296421051025391</v>
@@ -30545,7 +30892,7 @@
         <v>17</v>
       </c>
       <c r="HA52" s="1">
-        <v>0.077981650829315186</v>
+        <v>7.7981650829315186E-2</v>
       </c>
       <c r="HB52" s="1">
         <v>3</v>
@@ -30554,10 +30901,10 @@
         <v>81</v>
       </c>
       <c r="HD52" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -31055,10 +31402,10 @@
         <v>944</v>
       </c>
       <c r="FS53" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT53" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU53" t="s">
         <v>1</v>
@@ -31073,14 +31420,14 @@
         <v>81</v>
       </c>
       <c r="FY53" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="FZ53" s="1"/>
       <c r="GA53" s="1">
         <v>2025</v>
       </c>
       <c r="GB53" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="GC53" t="s">
         <v>941</v>
@@ -31137,7 +31484,7 @@
         <v>82.304000854492188</v>
       </c>
       <c r="GU53" s="1">
-        <v>23.261999130249024</v>
+        <v>23.261999130249023</v>
       </c>
       <c r="GV53" s="1">
         <v>2.5090000629425049</v>
@@ -31155,7 +31502,7 @@
         <v>9</v>
       </c>
       <c r="HA53" s="1">
-        <v>0.052941177040338516</v>
+        <v>5.2941177040338516E-2</v>
       </c>
       <c r="HB53" s="1">
         <v>3</v>
@@ -31164,10 +31511,10 @@
         <v>81</v>
       </c>
       <c r="HD53" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>12</v>
       </c>
@@ -31493,19 +31840,19 @@
         <v>944</v>
       </c>
       <c r="FS54" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT54" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="FU54" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="FV54" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="FW54" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="FX54" t="s">
         <v>82</v>
@@ -31518,7 +31865,7 @@
         <v>2025</v>
       </c>
       <c r="GB54" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="GC54" t="s">
         <v>941</v>
@@ -31566,7 +31913,7 @@
         <v>0.40799999237060547</v>
       </c>
       <c r="GR54" s="1">
-        <v>0.026000000536441803</v>
+        <v>2.6000000536441803E-2</v>
       </c>
       <c r="GS54" s="1">
         <v>362.26300048828125</v>
@@ -31581,7 +31928,7 @@
         <v>1.9299999475479126</v>
       </c>
       <c r="GW54" s="1">
-        <v>0.0060000000521540642</v>
+        <v>6.0000000521540642E-3</v>
       </c>
       <c r="GX54" s="1">
         <v>18.882282257080078</v>
@@ -31602,10 +31949,10 @@
         <v>82</v>
       </c>
       <c r="HD54" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -32085,19 +32432,19 @@
         <v>944</v>
       </c>
       <c r="FS55" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT55" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="FU55" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="FV55" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="FW55" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="FX55" t="s">
         <v>82</v>
@@ -32110,7 +32457,7 @@
         <v>2024</v>
       </c>
       <c r="GB55" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="GC55" t="s">
         <v>941</v>
@@ -32158,7 +32505,7 @@
         <v>0.48500001430511475</v>
       </c>
       <c r="GR55" s="1">
-        <v>0.041999999433755875</v>
+        <v>4.1999999433755875E-2</v>
       </c>
       <c r="GS55" s="1">
         <v>432.8280029296875</v>
@@ -32173,7 +32520,7 @@
         <v>2.2699999809265137</v>
       </c>
       <c r="GW55" s="1">
-        <v>0.0060000000521540642</v>
+        <v>6.0000000521540642E-3</v>
       </c>
       <c r="GX55" s="1">
         <v>17.688703536987305</v>
@@ -32194,10 +32541,10 @@
         <v>82</v>
       </c>
       <c r="HD55" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1</v>
       </c>
@@ -32677,32 +33024,32 @@
         <v>944</v>
       </c>
       <c r="FS56" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT56" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU56" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="FV56" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="FW56" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="FX56" t="s">
         <v>83</v>
       </c>
       <c r="FY56" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="FZ56" s="1"/>
       <c r="GA56" s="1">
         <v>2024</v>
       </c>
       <c r="GB56" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="GC56" t="s">
         <v>941</v>
@@ -32765,7 +33112,7 @@
         <v>2.1740000247955322</v>
       </c>
       <c r="GW56" s="1">
-        <v>0.054999999701976776</v>
+        <v>5.4999999701976776E-2</v>
       </c>
       <c r="GX56" s="1">
         <v>20.330165863037109</v>
@@ -32777,7 +33124,7 @@
         <v>6</v>
       </c>
       <c r="HA56" s="1">
-        <v>0.033149171620607376</v>
+        <v>3.3149171620607376E-2</v>
       </c>
       <c r="HB56" s="1">
         <v>2</v>
@@ -32786,10 +33133,10 @@
         <v>83</v>
       </c>
       <c r="HD56" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>16</v>
       </c>
@@ -33287,32 +33634,32 @@
         <v>944</v>
       </c>
       <c r="FS57" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT57" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU57" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="FV57" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="FW57" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="FX57" t="s">
         <v>83</v>
       </c>
       <c r="FY57" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="FZ57" s="1"/>
       <c r="GA57" s="1">
         <v>2025</v>
       </c>
       <c r="GB57" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="GC57" t="s">
         <v>941</v>
@@ -33351,7 +33698,7 @@
         <v>47</v>
       </c>
       <c r="GO57" s="1">
-        <v>0.92900002002716065</v>
+        <v>0.92900002002716064</v>
       </c>
       <c r="GP57" s="1">
         <v>1.1000000238418579</v>
@@ -33375,7 +33722,7 @@
         <v>2.2880001068115234</v>
       </c>
       <c r="GW57" s="1">
-        <v>0.046999998390674591</v>
+        <v>4.6999998390674591E-2</v>
       </c>
       <c r="GX57" s="1">
         <v>20.606025695800781</v>
@@ -33387,7 +33734,7 @@
         <v>6</v>
       </c>
       <c r="HA57" s="1">
-        <v>0.038461539894342423</v>
+        <v>3.8461539894342422E-2</v>
       </c>
       <c r="HB57" s="1">
         <v>2</v>
@@ -33396,10 +33743,10 @@
         <v>83</v>
       </c>
       <c r="HD57" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1</v>
       </c>
@@ -33879,32 +34226,32 @@
         <v>944</v>
       </c>
       <c r="FS58" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT58" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU58" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="FV58" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="FW58" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="FX58" t="s">
         <v>84</v>
       </c>
       <c r="FY58" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="FZ58" s="1"/>
       <c r="GA58" s="1">
         <v>2024</v>
       </c>
       <c r="GB58" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="GC58" t="s">
         <v>941</v>
@@ -33946,7 +34293,7 @@
         <v>1.0559999942779541</v>
       </c>
       <c r="GP58" s="1">
-        <v>1.1920000314712525</v>
+        <v>1.1920000314712524</v>
       </c>
       <c r="GQ58" s="1">
         <v>0.76399999856948853</v>
@@ -33967,7 +34314,7 @@
         <v>2.4170000553131104</v>
       </c>
       <c r="GW58" s="1">
-        <v>0.037000000476837158</v>
+        <v>3.7000000476837158E-2</v>
       </c>
       <c r="GX58" s="1">
         <v>16.65159797668457</v>
@@ -33988,10 +34335,10 @@
         <v>84</v>
       </c>
       <c r="HD58" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -34489,32 +34836,32 @@
         <v>944</v>
       </c>
       <c r="FS59" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT59" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU59" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="FV59" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="FW59" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="FX59" t="s">
         <v>84</v>
       </c>
       <c r="FY59" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="FZ59" s="1"/>
       <c r="GA59" s="1">
         <v>2025</v>
       </c>
       <c r="GB59" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="GC59" t="s">
         <v>941</v>
@@ -34577,7 +34924,7 @@
         <v>2.1359999179840088</v>
       </c>
       <c r="GW59" s="1">
-        <v>0.035999998450279236</v>
+        <v>3.5999998450279236E-2</v>
       </c>
       <c r="GX59" s="1">
         <v>17.817279815673828</v>
@@ -34598,10 +34945,10 @@
         <v>84</v>
       </c>
       <c r="HD59" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -35041,7 +35388,7 @@
         <v>0</v>
       </c>
       <c r="EY60" s="1">
-        <v>0.00089916441356763244</v>
+        <v>8.9916441356763244E-4</v>
       </c>
       <c r="EZ60" t="s">
         <v>524</v>
@@ -35099,32 +35446,32 @@
         <v>944</v>
       </c>
       <c r="FS60" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT60" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU60" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="FV60" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="FW60" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="FX60" t="s">
         <v>85</v>
       </c>
       <c r="FY60" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="FZ60" s="1"/>
       <c r="GA60" s="1">
         <v>2025</v>
       </c>
       <c r="GB60" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="GC60" t="s">
         <v>941</v>
@@ -35163,7 +35510,7 @@
         <v>84</v>
       </c>
       <c r="GO60" s="1">
-        <v>0.94999998807907105</v>
+        <v>0.94999998807907104</v>
       </c>
       <c r="GP60" s="1">
         <v>1.0149999856948853</v>
@@ -35187,7 +35534,7 @@
         <v>4.9479999542236328</v>
       </c>
       <c r="GW60" s="1">
-        <v>0.083999998867511749</v>
+        <v>8.3999998867511749E-2</v>
       </c>
       <c r="GX60" s="1">
         <v>29.218954086303711</v>
@@ -35208,10 +35555,10 @@
         <v>85</v>
       </c>
       <c r="HD60" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1</v>
       </c>
@@ -35691,32 +36038,32 @@
         <v>944</v>
       </c>
       <c r="FS61" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT61" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU61" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="FV61" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="FW61" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="FX61" t="s">
         <v>85</v>
       </c>
       <c r="FY61" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="FZ61" s="1"/>
       <c r="GA61" s="1">
         <v>2024</v>
       </c>
       <c r="GB61" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="GC61" t="s">
         <v>941</v>
@@ -35755,7 +36102,7 @@
         <v>220</v>
       </c>
       <c r="GO61" s="1">
-        <v>1.1920000314712525</v>
+        <v>1.1920000314712524</v>
       </c>
       <c r="GP61" s="1">
         <v>1.0900000333786011</v>
@@ -35791,7 +36138,7 @@
         <v>17</v>
       </c>
       <c r="HA61" s="1">
-        <v>0.066666670143604279</v>
+        <v>6.6666670143604279E-2</v>
       </c>
       <c r="HB61" s="1">
         <v>3</v>
@@ -35800,10 +36147,10 @@
         <v>85</v>
       </c>
       <c r="HD61" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1</v>
       </c>
@@ -36115,32 +36462,32 @@
         <v>944</v>
       </c>
       <c r="FS62" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT62" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU62" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="FV62" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="FW62" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="FX62" t="s">
         <v>86</v>
       </c>
       <c r="FY62" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="FZ62" s="1"/>
       <c r="GA62" s="1">
         <v>2024</v>
       </c>
       <c r="GB62" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="GC62" t="s">
         <v>941</v>
@@ -36203,7 +36550,7 @@
         <v>1.4639999866485596</v>
       </c>
       <c r="GW62" s="1">
-        <v>0.20999999344348908</v>
+        <v>0.20999999344348907</v>
       </c>
       <c r="GX62" s="1">
         <v>19.478366851806641</v>
@@ -36215,7 +36562,7 @@
         <v>7</v>
       </c>
       <c r="HA62" s="1">
-        <v>0.071428574621677399</v>
+        <v>7.1428574621677399E-2</v>
       </c>
       <c r="HB62" s="1">
         <v>1</v>
@@ -36224,10 +36571,10 @@
         <v>86</v>
       </c>
       <c r="HD62" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -36553,32 +36900,32 @@
         <v>944</v>
       </c>
       <c r="FS63" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT63" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU63" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="FV63" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="FW63" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="FX63" t="s">
         <v>86</v>
       </c>
       <c r="FY63" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="FZ63" s="1"/>
       <c r="GA63" s="1">
         <v>2025</v>
       </c>
       <c r="GB63" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="GC63" t="s">
         <v>941</v>
@@ -36653,7 +37000,7 @@
         <v>6</v>
       </c>
       <c r="HA63" s="1">
-        <v>0.068965516984462738</v>
+        <v>6.8965516984462738E-2</v>
       </c>
       <c r="HB63" s="1">
         <v>1</v>
@@ -36662,10 +37009,10 @@
         <v>86</v>
       </c>
       <c r="HD63" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1</v>
       </c>
@@ -37145,32 +37492,32 @@
         <v>944</v>
       </c>
       <c r="FS64" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT64" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU64" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="FV64" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="FW64" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="FX64" t="s">
         <v>87</v>
       </c>
       <c r="FY64" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="FZ64" s="1"/>
       <c r="GA64" s="1">
         <v>2024</v>
       </c>
       <c r="GB64" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="GC64" t="s">
         <v>941</v>
@@ -37218,7 +37565,7 @@
         <v>0.3880000114440918</v>
       </c>
       <c r="GR64" s="1">
-        <v>0.087999999523162842</v>
+        <v>8.7999999523162842E-2</v>
       </c>
       <c r="GS64" s="1">
         <v>378.50201416015625</v>
@@ -37233,7 +37580,7 @@
         <v>1.2690000534057617</v>
       </c>
       <c r="GW64" s="1">
-        <v>0.041999999433755875</v>
+        <v>4.1999999433755875E-2</v>
       </c>
       <c r="GX64" s="1">
         <v>12.537777900695801</v>
@@ -37245,7 +37592,7 @@
         <v>1</v>
       </c>
       <c r="HA64" s="1">
-        <v>0.018518518656492233</v>
+        <v>1.8518518656492233E-2</v>
       </c>
       <c r="HB64" s="1">
         <v>1</v>
@@ -37254,10 +37601,10 @@
         <v>87</v>
       </c>
       <c r="HD64" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2</v>
       </c>
@@ -37583,32 +37930,32 @@
         <v>944</v>
       </c>
       <c r="FS65" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT65" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU65" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="FV65" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="FW65" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="FX65" t="s">
         <v>87</v>
       </c>
       <c r="FY65" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="FZ65" s="1"/>
       <c r="GA65" s="1">
         <v>2025</v>
       </c>
       <c r="GB65" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="GC65" t="s">
         <v>941</v>
@@ -37656,7 +38003,7 @@
         <v>0.24099999666213989</v>
       </c>
       <c r="GR65" s="1">
-        <v>0.032999999821186066</v>
+        <v>3.2999999821186066E-2</v>
       </c>
       <c r="GS65" s="1">
         <v>226.51800537109375</v>
@@ -37671,7 +38018,7 @@
         <v>1.031999945640564</v>
       </c>
       <c r="GW65" s="1">
-        <v>0.067000001668930054</v>
+        <v>6.7000001668930054E-2</v>
       </c>
       <c r="GX65" s="1">
         <v>16.316774368286133</v>
@@ -37683,7 +38030,7 @@
         <v>2</v>
       </c>
       <c r="HA65" s="1">
-        <v>0.032258063554763794</v>
+        <v>3.2258063554763794E-2</v>
       </c>
       <c r="HB65" s="1">
         <v>1</v>
@@ -37692,10 +38039,10 @@
         <v>87</v>
       </c>
       <c r="HD65" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1</v>
       </c>
@@ -37975,10 +38322,10 @@
         <v>1</v>
       </c>
       <c r="FS66" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT66" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU66" t="s">
         <v>1</v>
@@ -38032,10 +38379,10 @@
         <v>88</v>
       </c>
       <c r="HD66" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1</v>
       </c>
@@ -38288,7 +38635,7 @@
         <v>18.129999160766602</v>
       </c>
       <c r="ET67" s="1">
-        <v>-7.0399999618530274</v>
+        <v>-7.0399999618530273</v>
       </c>
       <c r="EU67" s="1">
         <v>7</v>
@@ -38361,16 +38708,16 @@
         <v>947</v>
       </c>
       <c r="FS67" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT67" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU67" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="FV67" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="FW67" t="s">
         <v>1</v>
@@ -38386,7 +38733,7 @@
         <v>2025</v>
       </c>
       <c r="GB67" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="GC67" t="s">
         <v>941</v>
@@ -38428,10 +38775,10 @@
         <v>1.1599999666213989</v>
       </c>
       <c r="GP67" s="1">
-        <v>0.97899997234344483</v>
+        <v>0.97899997234344482</v>
       </c>
       <c r="GQ67" s="1">
-        <v>0.86500000953674317</v>
+        <v>0.86500000953674316</v>
       </c>
       <c r="GR67" s="1">
         <v>0.32300001382827759</v>
@@ -38449,7 +38796,7 @@
         <v>1.9199999570846558</v>
       </c>
       <c r="GW67" s="1">
-        <v>0.035000000149011612</v>
+        <v>3.5000000149011612E-2</v>
       </c>
       <c r="GX67" s="1">
         <v>18.997688293457031</v>
@@ -38461,7 +38808,7 @@
         <v>3</v>
       </c>
       <c r="HA67" s="1">
-        <v>0.01875000074505806</v>
+        <v>1.875000074505806E-2</v>
       </c>
       <c r="HB67" s="1">
         <v>1</v>
@@ -38470,10 +38817,10 @@
         <v>88</v>
       </c>
       <c r="HD67" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -38953,19 +39300,19 @@
         <v>944</v>
       </c>
       <c r="FS68" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT68" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="FU68" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="FV68" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="FW68" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="FX68" t="s">
         <v>90</v>
@@ -38978,7 +39325,7 @@
         <v>2024</v>
       </c>
       <c r="GB68" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="GC68" t="s">
         <v>941</v>
@@ -39026,7 +39373,7 @@
         <v>0.49300000071525574</v>
       </c>
       <c r="GR68" s="1">
-        <v>0.093999996781349182</v>
+        <v>9.3999996781349182E-2</v>
       </c>
       <c r="GS68" s="1">
         <v>397.99099731445313</v>
@@ -39053,7 +39400,7 @@
         <v>1</v>
       </c>
       <c r="HA68" s="1">
-        <v>0.0076335878111422062</v>
+        <v>7.6335878111422062E-3</v>
       </c>
       <c r="HB68" s="1">
         <v>1</v>
@@ -39062,10 +39409,10 @@
         <v>90</v>
       </c>
       <c r="HD68" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -39391,19 +39738,19 @@
         <v>944</v>
       </c>
       <c r="FS69" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT69" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="FU69" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="FV69" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="FW69" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="FX69" t="s">
         <v>90</v>
@@ -39416,7 +39763,7 @@
         <v>2025</v>
       </c>
       <c r="GB69" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="GC69" t="s">
         <v>941</v>
@@ -39458,13 +39805,13 @@
         <v>0.67500001192092896</v>
       </c>
       <c r="GP69" s="1">
-        <v>0.72899997234344483</v>
+        <v>0.72899997234344482</v>
       </c>
       <c r="GQ69" s="1">
         <v>0.44200000166893005</v>
       </c>
       <c r="GR69" s="1">
-        <v>0.064000003039836884</v>
+        <v>6.4000003039836884E-2</v>
       </c>
       <c r="GS69" s="1">
         <v>343.8599853515625</v>
@@ -39500,10 +39847,10 @@
         <v>90</v>
       </c>
       <c r="HD69" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -39771,7 +40118,7 @@
         <v>0</v>
       </c>
       <c r="EY70" s="1">
-        <v>0.0020676641725003719</v>
+        <v>2.0676641725003719E-3</v>
       </c>
       <c r="EZ70" t="s">
         <v>524</v>
@@ -39829,32 +40176,32 @@
         <v>944</v>
       </c>
       <c r="FS70" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT70" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU70" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="FV70" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="FW70" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="FX70" t="s">
         <v>91</v>
       </c>
       <c r="FY70" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="FZ70" s="1"/>
       <c r="GA70" s="1">
         <v>2025</v>
       </c>
       <c r="GB70" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="GC70" t="s">
         <v>941</v>
@@ -39938,10 +40285,10 @@
         <v>91</v>
       </c>
       <c r="HD70" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1</v>
       </c>
@@ -40363,7 +40710,7 @@
         <v>0</v>
       </c>
       <c r="EY71" s="1">
-        <v>0.0011151088401675224</v>
+        <v>1.1151088401675224E-3</v>
       </c>
       <c r="EZ71" t="s">
         <v>524</v>
@@ -40421,32 +40768,32 @@
         <v>944</v>
       </c>
       <c r="FS71" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT71" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU71" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="FV71" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="FW71" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="FX71" t="s">
         <v>91</v>
       </c>
       <c r="FY71" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="FZ71" s="1"/>
       <c r="GA71" s="1">
         <v>2024</v>
       </c>
       <c r="GB71" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="GC71" t="s">
         <v>941</v>
@@ -40488,7 +40835,7 @@
         <v>1.7829999923706055</v>
       </c>
       <c r="GP71" s="1">
-        <v>1.5670000314712525</v>
+        <v>1.5670000314712524</v>
       </c>
       <c r="GQ71" s="1">
         <v>1.5420000553131104</v>
@@ -40530,10 +40877,10 @@
         <v>91</v>
       </c>
       <c r="HD71" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1</v>
       </c>
@@ -40849,32 +41196,32 @@
         <v>944</v>
       </c>
       <c r="FS72" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT72" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU72" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="FV72" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="FW72" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="FX72" t="s">
         <v>92</v>
       </c>
       <c r="FY72" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="FZ72" s="1"/>
       <c r="GA72" s="1">
         <v>2024</v>
       </c>
       <c r="GB72" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="GC72" t="s">
         <v>941</v>
@@ -40958,10 +41305,10 @@
         <v>92</v>
       </c>
       <c r="HD72" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -41287,32 +41634,32 @@
         <v>944</v>
       </c>
       <c r="FS73" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT73" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU73" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="FV73" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="FW73" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="FX73" t="s">
         <v>92</v>
       </c>
       <c r="FY73" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="FZ73" s="1"/>
       <c r="GA73" s="1">
         <v>2025</v>
       </c>
       <c r="GB73" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="GC73" t="s">
         <v>941</v>
@@ -41396,10 +41743,10 @@
         <v>92</v>
       </c>
       <c r="HD73" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -41725,32 +42072,32 @@
         <v>944</v>
       </c>
       <c r="FS74" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT74" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU74" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="FV74" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="FW74" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="FX74" t="s">
         <v>93</v>
       </c>
       <c r="FY74" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="FZ74" s="1"/>
       <c r="GA74" s="1">
         <v>2025</v>
       </c>
       <c r="GB74" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="GC74" t="s">
         <v>941</v>
@@ -41834,10 +42181,10 @@
         <v>93</v>
       </c>
       <c r="HD74" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1</v>
       </c>
@@ -42293,32 +42640,32 @@
         <v>944</v>
       </c>
       <c r="FS75" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT75" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU75" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="FV75" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="FW75" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="FX75" t="s">
         <v>93</v>
       </c>
       <c r="FY75" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="FZ75" s="1"/>
       <c r="GA75" s="1">
         <v>2024</v>
       </c>
       <c r="GB75" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="GC75" t="s">
         <v>941</v>
@@ -42363,7 +42710,7 @@
         <v>1.4029999971389771</v>
       </c>
       <c r="GQ75" s="1">
-        <v>1.2339999675750733</v>
+        <v>1.2339999675750732</v>
       </c>
       <c r="GR75" s="1">
         <v>0.24699999392032623</v>
@@ -42402,10 +42749,10 @@
         <v>93</v>
       </c>
       <c r="HD75" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>1</v>
       </c>
@@ -42827,7 +43174,7 @@
         <v>0</v>
       </c>
       <c r="EY76" s="1">
-        <v>1.0329889059066773</v>
+        <v>1.0329889059066772</v>
       </c>
       <c r="EZ76" t="s">
         <v>524</v>
@@ -42885,32 +43232,32 @@
         <v>944</v>
       </c>
       <c r="FS76" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT76" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU76" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="FV76" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="FW76" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="FX76" t="s">
         <v>95</v>
       </c>
       <c r="FY76" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="FZ76" s="1"/>
       <c r="GA76" s="1">
         <v>2024</v>
       </c>
       <c r="GB76" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="GC76" t="s">
         <v>941</v>
@@ -42994,10 +43341,10 @@
         <v>95</v>
       </c>
       <c r="HD76" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>10</v>
       </c>
@@ -43323,32 +43670,32 @@
         <v>944</v>
       </c>
       <c r="FS77" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT77" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU77" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="FV77" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="FW77" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="FX77" t="s">
         <v>95</v>
       </c>
       <c r="FY77" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="FZ77" s="1"/>
       <c r="GA77" s="1">
         <v>2025</v>
       </c>
       <c r="GB77" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="GC77" t="s">
         <v>941</v>
@@ -43423,7 +43770,7 @@
         <v>15</v>
       </c>
       <c r="HA77" s="1">
-        <v>0.098039217293262482</v>
+        <v>9.8039217293262482E-2</v>
       </c>
       <c r="HB77" s="1">
         <v>3</v>
@@ -43432,10 +43779,10 @@
         <v>95</v>
       </c>
       <c r="HD77" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1</v>
       </c>
@@ -43842,7 +44189,7 @@
         <v>18.559999465942383</v>
       </c>
       <c r="ET78" s="1">
-        <v>7.9000000953674317</v>
+        <v>7.9000000953674316</v>
       </c>
       <c r="EU78" s="1">
         <v>158</v>
@@ -43915,32 +44262,32 @@
         <v>944</v>
       </c>
       <c r="FS78" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT78" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU78" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="FV78" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="FW78" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="FX78" t="s">
         <v>96</v>
       </c>
       <c r="FY78" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="FZ78" s="1"/>
       <c r="GA78" s="1">
         <v>2024</v>
       </c>
       <c r="GB78" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="GC78" t="s">
         <v>941</v>
@@ -44015,7 +44362,7 @@
         <v>6</v>
       </c>
       <c r="HA78" s="1">
-        <v>0.054054055362939835</v>
+        <v>5.4054055362939835E-2</v>
       </c>
       <c r="HB78" s="1">
         <v>3</v>
@@ -44024,10 +44371,10 @@
         <v>96</v>
       </c>
       <c r="HD78" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>20</v>
       </c>
@@ -44525,32 +44872,32 @@
         <v>944</v>
       </c>
       <c r="FS79" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT79" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU79" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="FV79" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="FW79" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="FX79" t="s">
         <v>96</v>
       </c>
       <c r="FY79" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="FZ79" s="1"/>
       <c r="GA79" s="1">
         <v>2025</v>
       </c>
       <c r="GB79" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="GC79" t="s">
         <v>941</v>
@@ -44625,7 +44972,7 @@
         <v>28</v>
       </c>
       <c r="HA79" s="1">
-        <v>0.24778760969638825</v>
+        <v>0.24778760969638824</v>
       </c>
       <c r="HB79" s="1">
         <v>3</v>
@@ -44634,10 +44981,10 @@
         <v>96</v>
       </c>
       <c r="HD79" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1</v>
       </c>
@@ -45117,32 +45464,32 @@
         <v>944</v>
       </c>
       <c r="FS80" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT80" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU80" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="FV80" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="FW80" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="FX80" t="s">
         <v>98</v>
       </c>
       <c r="FY80" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="FZ80" s="1"/>
       <c r="GA80" s="1">
         <v>2024</v>
       </c>
       <c r="GB80" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="GC80" t="s">
         <v>941</v>
@@ -45205,7 +45552,7 @@
         <v>4.629000186920166</v>
       </c>
       <c r="GW80" s="1">
-        <v>0.097000002861022949</v>
+        <v>9.7000002861022949E-2</v>
       </c>
       <c r="GX80" s="1">
         <v>19.474170684814453</v>
@@ -45226,10 +45573,10 @@
         <v>98</v>
       </c>
       <c r="HD80" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -45555,32 +45902,32 @@
         <v>944</v>
       </c>
       <c r="FS81" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT81" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU81" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="FV81" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="FW81" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="FX81" t="s">
         <v>98</v>
       </c>
       <c r="FY81" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="FZ81" s="1"/>
       <c r="GA81" s="1">
         <v>2025</v>
       </c>
       <c r="GB81" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="GC81" t="s">
         <v>941</v>
@@ -45655,7 +46002,7 @@
         <v>2</v>
       </c>
       <c r="HA81" s="1">
-        <v>0.011764706112444401</v>
+        <v>1.1764706112444401E-2</v>
       </c>
       <c r="HB81" s="1">
         <v>3</v>
@@ -45664,10 +46011,10 @@
         <v>98</v>
       </c>
       <c r="HD81" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1</v>
       </c>
@@ -46111,10 +46458,10 @@
         <v>1</v>
       </c>
       <c r="FS82" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT82" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU82" t="s">
         <v>1</v>
@@ -46168,10 +46515,10 @@
         <v>100</v>
       </c>
       <c r="HD82" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -46461,10 +46808,10 @@
         <v>1</v>
       </c>
       <c r="FS83" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT83" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU83" t="s">
         <v>1</v>
@@ -46518,10 +46865,10 @@
         <v>100</v>
       </c>
       <c r="HD83" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1</v>
       </c>
@@ -47001,32 +47348,32 @@
         <v>944</v>
       </c>
       <c r="FS84" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT84" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU84" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="FV84" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="FW84" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="FX84" t="s">
         <v>101</v>
       </c>
       <c r="FY84" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="FZ84" s="1"/>
       <c r="GA84" s="1">
         <v>2024</v>
       </c>
       <c r="GB84" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="GC84" t="s">
         <v>941</v>
@@ -47071,7 +47418,7 @@
         <v>0.95800000429153442</v>
       </c>
       <c r="GQ84" s="1">
-        <v>0.67900002002716065</v>
+        <v>0.67900002002716064</v>
       </c>
       <c r="GR84" s="1">
         <v>0.15999999642372131</v>
@@ -47110,10 +47457,10 @@
         <v>101</v>
       </c>
       <c r="HD84" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>22</v>
       </c>
@@ -47553,7 +47900,7 @@
         <v>0</v>
       </c>
       <c r="EY85" s="1">
-        <v>1.0003193616867066</v>
+        <v>1.0003193616867065</v>
       </c>
       <c r="EZ85" t="s">
         <v>524</v>
@@ -47611,32 +47958,32 @@
         <v>944</v>
       </c>
       <c r="FS85" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT85" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="FU85" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="FV85" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="FW85" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="FX85" t="s">
         <v>101</v>
       </c>
       <c r="FY85" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="FZ85" s="1"/>
       <c r="GA85" s="1">
         <v>2025</v>
       </c>
       <c r="GB85" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="GC85" t="s">
         <v>941</v>
@@ -47699,7 +48046,7 @@
         <v>2.0920000076293945</v>
       </c>
       <c r="GW85" s="1">
-        <v>0.18799999356269837</v>
+        <v>0.18799999356269836</v>
       </c>
       <c r="GX85" s="1">
         <v>24.515678405761719</v>
@@ -47720,10 +48067,10 @@
         <v>101</v>
       </c>
       <c r="HD85" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -48013,10 +48360,10 @@
         <v>1</v>
       </c>
       <c r="FS86" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT86" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="FU86" t="s">
         <v>1</v>
@@ -48070,10 +48417,10 @@
         <v>102</v>
       </c>
       <c r="HD86" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1</v>
       </c>
@@ -48493,10 +48840,10 @@
         <v>1</v>
       </c>
       <c r="FS87" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT87" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="FU87" t="s">
         <v>1</v>
@@ -48550,10 +48897,10 @@
         <v>102</v>
       </c>
       <c r="HD87" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1</v>
       </c>
@@ -49033,32 +49380,32 @@
         <v>944</v>
       </c>
       <c r="FS88" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT88" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="FU88" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="FV88" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="FW88" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="FX88" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="FY88" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="FZ88" s="1"/>
       <c r="GA88" s="1">
         <v>2024</v>
       </c>
       <c r="GB88" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="GC88" t="s">
         <v>941</v>
@@ -49121,7 +49468,7 @@
         <v>2.4509999752044678</v>
       </c>
       <c r="GW88" s="1">
-        <v>0.079999998211860657</v>
+        <v>7.9999998211860657E-2</v>
       </c>
       <c r="GX88" s="1">
         <v>19.729082107543945</v>
@@ -49133,19 +49480,19 @@
         <v>3</v>
       </c>
       <c r="HA88" s="1">
-        <v>0.030612245202064514</v>
+        <v>3.0612245202064514E-2</v>
       </c>
       <c r="HB88" s="1">
         <v>1</v>
       </c>
       <c r="HC88" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="HD88" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1</v>
       </c>
@@ -49471,32 +49818,32 @@
         <v>944</v>
       </c>
       <c r="FS89" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT89" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="FU89" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="FV89" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="FW89" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="FX89" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="FY89" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="FZ89" s="1"/>
       <c r="GA89" s="1">
         <v>2025</v>
       </c>
       <c r="GB89" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="GC89" t="s">
         <v>941</v>
@@ -49559,7 +49906,7 @@
         <v>2.7390000820159912</v>
       </c>
       <c r="GW89" s="1">
-        <v>0.082000002264976501</v>
+        <v>8.2000002264976501E-2</v>
       </c>
       <c r="GX89" s="1">
         <v>20.538600921630859</v>
@@ -49571,19 +49918,19 @@
         <v>2</v>
       </c>
       <c r="HA89" s="1">
-        <v>0.019999999552965164</v>
+        <v>1.9999999552965164E-2</v>
       </c>
       <c r="HB89" s="1">
         <v>1</v>
       </c>
       <c r="HC89" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="HD89" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>24</v>
       </c>
@@ -49909,19 +50256,19 @@
         <v>944</v>
       </c>
       <c r="FS90" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT90" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU90" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="FV90" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="FW90" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="FX90" t="s">
         <v>105</v>
@@ -49934,7 +50281,7 @@
         <v>2025</v>
       </c>
       <c r="GB90" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="GC90" t="s">
         <v>941</v>
@@ -50009,7 +50356,7 @@
         <v>9</v>
       </c>
       <c r="HA90" s="1">
-        <v>0.065217390656471253</v>
+        <v>6.5217390656471252E-2</v>
       </c>
       <c r="HB90" s="1">
         <v>3</v>
@@ -50018,10 +50365,10 @@
         <v>105</v>
       </c>
       <c r="HD90" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1</v>
       </c>
@@ -50501,19 +50848,19 @@
         <v>944</v>
       </c>
       <c r="FS91" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT91" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU91" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="FV91" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="FW91" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="FX91" t="s">
         <v>105</v>
@@ -50526,7 +50873,7 @@
         <v>2024</v>
       </c>
       <c r="GB91" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="GC91" t="s">
         <v>941</v>
@@ -50601,7 +50948,7 @@
         <v>3</v>
       </c>
       <c r="HA91" s="1">
-        <v>0.018518518656492233</v>
+        <v>1.8518518656492233E-2</v>
       </c>
       <c r="HB91" s="1">
         <v>3</v>
@@ -50610,10 +50957,10 @@
         <v>105</v>
       </c>
       <c r="HD91" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>12</v>
       </c>
@@ -50939,32 +51286,32 @@
         <v>944</v>
       </c>
       <c r="FS92" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT92" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU92" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="FV92" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="FW92" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="FX92" t="s">
         <v>106</v>
       </c>
       <c r="FY92" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="FZ92" s="1"/>
       <c r="GA92" s="1">
         <v>2025</v>
       </c>
       <c r="GB92" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="GC92" t="s">
         <v>941</v>
@@ -51024,7 +51371,7 @@
         <v>25.010000228881836</v>
       </c>
       <c r="GV92" s="1">
-        <v>5.4840002059936524</v>
+        <v>5.4840002059936523</v>
       </c>
       <c r="GW92" s="1">
         <v>0.11699999868869781</v>
@@ -51039,7 +51386,7 @@
         <v>1</v>
       </c>
       <c r="HA92" s="1">
-        <v>0.005681818351149559</v>
+        <v>5.681818351149559E-3</v>
       </c>
       <c r="HB92" s="1">
         <v>2</v>
@@ -51048,10 +51395,10 @@
         <v>106</v>
       </c>
       <c r="HD92" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1</v>
       </c>
@@ -51531,32 +51878,32 @@
         <v>944</v>
       </c>
       <c r="FS93" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT93" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="FU93" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="FV93" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="FW93" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="FX93" t="s">
         <v>106</v>
       </c>
       <c r="FY93" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="FZ93" s="1"/>
       <c r="GA93" s="1">
         <v>2024</v>
       </c>
       <c r="GB93" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="GC93" t="s">
         <v>941</v>
@@ -51595,7 +51942,7 @@
         <v>100</v>
       </c>
       <c r="GO93" s="1">
-        <v>0.69999998807907105</v>
+        <v>0.69999998807907104</v>
       </c>
       <c r="GP93" s="1">
         <v>1.1940000057220459</v>
@@ -51604,7 +51951,7 @@
         <v>0.91100001335144043</v>
       </c>
       <c r="GR93" s="1">
-        <v>0.34499999880790711</v>
+        <v>0.3449999988079071</v>
       </c>
       <c r="GS93" s="1">
         <v>548.39599609375</v>
@@ -51640,10 +51987,10 @@
         <v>106</v>
       </c>
       <c r="HD93" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1</v>
       </c>
@@ -52123,32 +52470,32 @@
         <v>944</v>
       </c>
       <c r="FS94" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="FT94" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="FU94" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="FV94" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="FW94" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="FX94" t="s">
         <v>107</v>
       </c>
       <c r="FY94" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="FZ94" s="1"/>
       <c r="GA94" s="1">
         <v>2024</v>
       </c>
       <c r="GB94" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="GC94" t="s">
         <v>941</v>
@@ -52187,7 +52534,7 @@
         <v>45</v>
       </c>
       <c r="GO94" s="1">
-        <v>1.2480000257492066</v>
+        <v>1.2480000257492065</v>
       </c>
       <c r="GP94" s="1">
         <v>1.062999963760376</v>
@@ -52211,7 +52558,7 @@
         <v>3.1129999160766602</v>
       </c>
       <c r="GW94" s="1">
-        <v>0.045000001788139343</v>
+        <v>4.5000001788139343E-2</v>
       </c>
       <c r="GX94" s="1">
         <v>16.131690979003906</v>
@@ -52232,10 +52579,10 @@
         <v>107</v>
       </c>
       <c r="HD94" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>9</v>
       </c>
@@ -52561,32 +52908,32 @@
         <v>944</v>
       </c>
       <c r="FS95" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="FT95" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="FU95" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="FV95" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="FW95" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="FX95" t="s">
         <v>107</v>
       </c>
       <c r="FY95" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="FZ95" s="1"/>
       <c r="GA95" s="1">
         <v>2025</v>
       </c>
       <c r="GB95" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="GC95" t="s">
         <v>941</v>
@@ -52649,7 +52996,7 @@
         <v>3.0850000381469727</v>
       </c>
       <c r="GW95" s="1">
-        <v>0.070000000298023224</v>
+        <v>7.0000000298023224E-2</v>
       </c>
       <c r="GX95" s="1">
         <v>17.072822570800781</v>
@@ -52670,10 +53017,10 @@
         <v>107</v>
       </c>
       <c r="HD95" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>8</v>
       </c>
@@ -52963,10 +53310,10 @@
         <v>1</v>
       </c>
       <c r="FS96" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT96" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU96" t="s">
         <v>1</v>
@@ -53020,10 +53367,10 @@
         <v>108</v>
       </c>
       <c r="HD96" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1</v>
       </c>
@@ -53467,10 +53814,10 @@
         <v>1</v>
       </c>
       <c r="FS97" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT97" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="FU97" t="s">
         <v>1</v>
@@ -53524,10 +53871,10 @@
         <v>108</v>
       </c>
       <c r="HD97" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -53853,32 +54200,32 @@
         <v>944</v>
       </c>
       <c r="FS98" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT98" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="FU98" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="FV98" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="FW98" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="FX98" t="s">
         <v>109</v>
       </c>
       <c r="FY98" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="FZ98" s="1"/>
       <c r="GA98" s="1">
         <v>2025</v>
       </c>
       <c r="GB98" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="GC98" t="s">
         <v>941</v>
@@ -53962,10 +54309,10 @@
         <v>109</v>
       </c>
       <c r="HD98" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1</v>
       </c>
@@ -54445,32 +54792,32 @@
         <v>944</v>
       </c>
       <c r="FS99" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT99" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="FU99" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="FV99" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="FW99" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="FX99" t="s">
         <v>109</v>
       </c>
       <c r="FY99" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="FZ99" s="1"/>
       <c r="GA99" s="1">
         <v>2024</v>
       </c>
       <c r="GB99" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="GC99" t="s">
         <v>941</v>
@@ -54512,7 +54859,7 @@
         <v>1.0499999523162842</v>
       </c>
       <c r="GP99" s="1">
-        <v>1.472000002861023</v>
+        <v>1.4720000028610229</v>
       </c>
       <c r="GQ99" s="1">
         <v>0.69199997186660767</v>
@@ -54533,7 +54880,7 @@
         <v>3.6189999580383301</v>
       </c>
       <c r="GW99" s="1">
-        <v>0.096000000834465027</v>
+        <v>9.6000000834465027E-2</v>
       </c>
       <c r="GX99" s="1">
         <v>18.475908279418945</v>
@@ -54554,10 +54901,10 @@
         <v>109</v>
       </c>
       <c r="HD99" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>8</v>
       </c>
@@ -54847,10 +55194,10 @@
         <v>1</v>
       </c>
       <c r="FS100" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT100" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="FU100" t="s">
         <v>1</v>
@@ -54904,10 +55251,10 @@
         <v>110</v>
       </c>
       <c r="HD100" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>1</v>
       </c>
@@ -55351,10 +55698,10 @@
         <v>1</v>
       </c>
       <c r="FS101" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT101" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="FU101" t="s">
         <v>1</v>
@@ -55408,10 +55755,10 @@
         <v>110</v>
       </c>
       <c r="HD101" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>10</v>
       </c>
@@ -55664,7 +56011,7 @@
         <v>20.579999923706055</v>
       </c>
       <c r="ET102" s="1">
-        <v>-0.94999998807907105</v>
+        <v>-0.94999998807907104</v>
       </c>
       <c r="EU102" s="1">
         <v>6</v>
@@ -55737,19 +56084,19 @@
         <v>944</v>
       </c>
       <c r="FS102" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT102" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="FU102" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="FV102" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="FW102" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="FX102" t="s">
         <v>112</v>
@@ -55762,7 +56109,7 @@
         <v>2025</v>
       </c>
       <c r="GB102" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="GC102" t="s">
         <v>941</v>
@@ -55837,7 +56184,7 @@
         <v>1</v>
       </c>
       <c r="HA102" s="1">
-        <v>0.0083333337679505348</v>
+        <v>8.3333337679505348E-3</v>
       </c>
       <c r="HB102" s="1">
         <v>2</v>
@@ -55846,10 +56193,10 @@
         <v>112</v>
       </c>
       <c r="HD102" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1</v>
       </c>
@@ -56329,19 +56676,19 @@
         <v>944</v>
       </c>
       <c r="FS103" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT103" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="FU103" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="FV103" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="FW103" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="FX103" t="s">
         <v>112</v>
@@ -56354,7 +56701,7 @@
         <v>2024</v>
       </c>
       <c r="GB103" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="GC103" t="s">
         <v>941</v>
@@ -56429,7 +56776,7 @@
         <v>6</v>
       </c>
       <c r="HA103" s="1">
-        <v>0.046153847128152847</v>
+        <v>4.6153847128152847E-2</v>
       </c>
       <c r="HB103" s="1">
         <v>2</v>
@@ -56438,10 +56785,10 @@
         <v>112</v>
       </c>
       <c r="HD103" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1</v>
       </c>
@@ -56921,19 +57268,19 @@
         <v>944</v>
       </c>
       <c r="FS104" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT104" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="FU104" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="FV104" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="FW104" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="FX104" t="s">
         <v>114</v>
@@ -56946,7 +57293,7 @@
         <v>2024</v>
       </c>
       <c r="GB104" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="GC104" t="s">
         <v>941</v>
@@ -57009,7 +57356,7 @@
         <v>3.9749999046325684</v>
       </c>
       <c r="GW104" s="1">
-        <v>0.059999998658895493</v>
+        <v>5.9999998658895493E-2</v>
       </c>
       <c r="GX104" s="1">
         <v>16.614835739135742</v>
@@ -57021,7 +57368,7 @@
         <v>2</v>
       </c>
       <c r="HA104" s="1">
-        <v>0.021978022530674934</v>
+        <v>2.1978022530674934E-2</v>
       </c>
       <c r="HB104" s="1">
         <v>2</v>
@@ -57030,10 +57377,10 @@
         <v>114</v>
       </c>
       <c r="HD104" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -57359,19 +57706,19 @@
         <v>944</v>
       </c>
       <c r="FS105" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT105" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="FU105" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="FV105" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="FW105" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="FX105" t="s">
         <v>114</v>
@@ -57384,7 +57731,7 @@
         <v>2025</v>
       </c>
       <c r="GB105" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="GC105" t="s">
         <v>941</v>
@@ -57429,7 +57776,7 @@
         <v>1.0659999847412109</v>
       </c>
       <c r="GQ105" s="1">
-        <v>0.60399997234344483</v>
+        <v>0.60399997234344482</v>
       </c>
       <c r="GR105" s="1">
         <v>0.19099999964237213</v>
@@ -57447,7 +57794,7 @@
         <v>4.7010002136230469</v>
       </c>
       <c r="GW105" s="1">
-        <v>0.094999998807907105</v>
+        <v>9.4999998807907104E-2</v>
       </c>
       <c r="GX105" s="1">
         <v>17.691389083862305</v>
@@ -57459,7 +57806,7 @@
         <v>2</v>
       </c>
       <c r="HA105" s="1">
-        <v>0.018518518656492233</v>
+        <v>1.8518518656492233E-2</v>
       </c>
       <c r="HB105" s="1">
         <v>2</v>
@@ -57468,10 +57815,10 @@
         <v>114</v>
       </c>
       <c r="HD105" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -57797,32 +58144,32 @@
         <v>944</v>
       </c>
       <c r="FS106" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT106" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU106" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="FV106" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="FW106" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="FX106" t="s">
         <v>115</v>
       </c>
       <c r="FY106" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="FZ106" s="1"/>
       <c r="GA106" s="1">
         <v>2025</v>
       </c>
       <c r="GB106" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="GC106" t="s">
         <v>941</v>
@@ -57897,7 +58244,7 @@
         <v>3</v>
       </c>
       <c r="HA106" s="1">
-        <v>0.015384615398943424</v>
+        <v>1.5384615398943424E-2</v>
       </c>
       <c r="HB106" s="1">
         <v>3</v>
@@ -57906,10 +58253,10 @@
         <v>115</v>
       </c>
       <c r="HD106" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1</v>
       </c>
@@ -58389,32 +58736,32 @@
         <v>944</v>
       </c>
       <c r="FS107" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT107" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU107" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="FV107" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="FW107" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="FX107" t="s">
         <v>115</v>
       </c>
       <c r="FY107" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="FZ107" s="1"/>
       <c r="GA107" s="1">
         <v>2024</v>
       </c>
       <c r="GB107" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="GC107" t="s">
         <v>941</v>
@@ -58498,10 +58845,10 @@
         <v>115</v>
       </c>
       <c r="HD107" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1</v>
       </c>
@@ -58945,10 +59292,10 @@
         <v>1</v>
       </c>
       <c r="FS108" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT108" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU108" t="s">
         <v>1</v>
@@ -59002,10 +59349,10 @@
         <v>116</v>
       </c>
       <c r="HD108" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>26</v>
       </c>
@@ -59295,10 +59642,10 @@
         <v>1</v>
       </c>
       <c r="FS109" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT109" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU109" t="s">
         <v>1</v>
@@ -59352,10 +59699,10 @@
         <v>116</v>
       </c>
       <c r="HD109" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1</v>
       </c>
@@ -59799,10 +60146,10 @@
         <v>1</v>
       </c>
       <c r="FS110" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT110" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU110" t="s">
         <v>1</v>
@@ -59856,10 +60203,10 @@
         <v>118</v>
       </c>
       <c r="HD110" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>27</v>
       </c>
@@ -60149,10 +60496,10 @@
         <v>1</v>
       </c>
       <c r="FS111" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="FT111" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="FU111" t="s">
         <v>1</v>
@@ -60206,10 +60553,10 @@
         <v>118</v>
       </c>
       <c r="HD111" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>28</v>
       </c>
@@ -60499,10 +60846,10 @@
         <v>1</v>
       </c>
       <c r="FS112" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT112" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="FU112" t="s">
         <v>1</v>
@@ -60556,10 +60903,10 @@
         <v>119</v>
       </c>
       <c r="HD112" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1</v>
       </c>
@@ -61003,10 +61350,10 @@
         <v>1</v>
       </c>
       <c r="FS113" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="FT113" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="FU113" t="s">
         <v>1</v>
@@ -61060,10 +61407,10 @@
         <v>119</v>
       </c>
       <c r="HD113" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1</v>
       </c>
@@ -61543,19 +61890,19 @@
         <v>944</v>
       </c>
       <c r="FS114" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT114" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU114" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="FV114" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="FW114" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="FX114" t="s">
         <v>120</v>
@@ -61568,7 +61915,7 @@
         <v>2024</v>
       </c>
       <c r="GB114" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="GC114" t="s">
         <v>941</v>
@@ -61610,7 +61957,7 @@
         <v>2.2599999904632568</v>
       </c>
       <c r="GP114" s="1">
-        <v>1.1649999618530274</v>
+        <v>1.1649999618530273</v>
       </c>
       <c r="GQ114" s="1">
         <v>1.2369999885559082</v>
@@ -61631,7 +61978,7 @@
         <v>8.0410003662109375</v>
       </c>
       <c r="GW114" s="1">
-        <v>0.21400000154972077</v>
+        <v>0.21400000154972076</v>
       </c>
       <c r="GX114" s="1">
         <v>34.974246978759766</v>
@@ -61643,7 +61990,7 @@
         <v>3</v>
       </c>
       <c r="HA114" s="1">
-        <v>0.016129031777381897</v>
+        <v>1.6129031777381897E-2</v>
       </c>
       <c r="HB114" s="1">
         <v>3</v>
@@ -61652,10 +61999,10 @@
         <v>120</v>
       </c>
       <c r="HD114" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>2</v>
       </c>
@@ -61981,19 +62328,19 @@
         <v>944</v>
       </c>
       <c r="FS115" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT115" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU115" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="FV115" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="FW115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="FX115" t="s">
         <v>120</v>
@@ -62006,7 +62353,7 @@
         <v>2025</v>
       </c>
       <c r="GB115" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="GC115" t="s">
         <v>941</v>
@@ -62081,7 +62428,7 @@
         <v>9</v>
       </c>
       <c r="HA115" s="1">
-        <v>0.044117648154497147</v>
+        <v>4.4117648154497147E-2</v>
       </c>
       <c r="HB115" s="1">
         <v>3</v>
@@ -62090,10 +62437,10 @@
         <v>120</v>
       </c>
       <c r="HD115" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -62533,7 +62880,7 @@
         <v>1</v>
       </c>
       <c r="EY116" s="1">
-        <v>0.070115216076374054</v>
+        <v>7.0115216076374054E-2</v>
       </c>
       <c r="EZ116" t="s">
         <v>524</v>
@@ -62591,32 +62938,32 @@
         <v>944</v>
       </c>
       <c r="FS116" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT116" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU116" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="FV116" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="FW116" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="FX116" t="s">
         <v>121</v>
       </c>
       <c r="FY116" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="FZ116" s="1"/>
       <c r="GA116" s="1">
         <v>2025</v>
       </c>
       <c r="GB116" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="GC116" t="s">
         <v>941</v>
@@ -62658,7 +63005,7 @@
         <v>0.82099997997283936</v>
       </c>
       <c r="GP116" s="1">
-        <v>1.2339999675750733</v>
+        <v>1.2339999675750732</v>
       </c>
       <c r="GQ116" s="1">
         <v>0.86699998378753662</v>
@@ -62679,7 +63026,7 @@
         <v>4.1279997825622559</v>
       </c>
       <c r="GW116" s="1">
-        <v>0.071000002324581146</v>
+        <v>7.1000002324581146E-2</v>
       </c>
       <c r="GX116" s="1">
         <v>16.656585693359375</v>
@@ -62700,10 +63047,10 @@
         <v>121</v>
       </c>
       <c r="HD116" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1</v>
       </c>
@@ -63183,32 +63530,32 @@
         <v>944</v>
       </c>
       <c r="FS117" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="FT117" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="FU117" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="FV117" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="FW117" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="FX117" t="s">
         <v>121</v>
       </c>
       <c r="FY117" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="FZ117" s="1"/>
       <c r="GA117" s="1">
         <v>2024</v>
       </c>
       <c r="GB117" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="GC117" t="s">
         <v>941</v>
@@ -63253,7 +63600,7 @@
         <v>1.1690000295639038</v>
       </c>
       <c r="GQ117" s="1">
-        <v>0.94999998807907105</v>
+        <v>0.94999998807907104</v>
       </c>
       <c r="GR117" s="1">
         <v>0.27700001001358032</v>
@@ -63271,7 +63618,7 @@
         <v>3.2950000762939453</v>
       </c>
       <c r="GW117" s="1">
-        <v>0.068000003695487976</v>
+        <v>6.8000003695487976E-2</v>
       </c>
       <c r="GX117" s="1">
         <v>15.912110328674316</v>
@@ -63283,7 +63630,7 @@
         <v>1</v>
       </c>
       <c r="HA117" s="1">
-        <v>0.0091743115335702896</v>
+        <v>9.1743115335702896E-3</v>
       </c>
       <c r="HB117" s="1">
         <v>2</v>
@@ -63292,10 +63639,10 @@
         <v>121</v>
       </c>
       <c r="HD117" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1</v>
       </c>
@@ -63775,19 +64122,19 @@
         <v>944</v>
       </c>
       <c r="FS118" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="FT118" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="FU118" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="FV118" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="FW118" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="FX118" t="s">
         <v>122</v>
@@ -63800,7 +64147,7 @@
         <v>2024</v>
       </c>
       <c r="GB118" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="GC118" t="s">
         <v>941</v>
@@ -63863,7 +64210,7 @@
         <v>1.4429999589920044</v>
       </c>
       <c r="GW118" s="1">
-        <v>0.043999999761581421</v>
+        <v>4.3999999761581421E-2</v>
       </c>
       <c r="GX118" s="1">
         <v>18.254062652587891</v>
@@ -63884,10 +64231,10 @@
         <v>122</v>
       </c>
       <c r="HD118" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>10</v>
       </c>
@@ -64213,19 +64560,19 @@
         <v>944</v>
       </c>
       <c r="FS119" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="FT119" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="FU119" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="FV119" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="FW119" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="FX119" t="s">
         <v>122</v>
@@ -64238,7 +64585,7 @@
         <v>2025</v>
       </c>
       <c r="GB119" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="GC119" t="s">
         <v>941</v>
@@ -64283,7 +64630,7 @@
         <v>0.34799998998641968</v>
       </c>
       <c r="GQ119" s="1">
-        <v>0.28099998831748963</v>
+        <v>0.28099998831748962</v>
       </c>
       <c r="GR119" s="1">
         <v>0.10300000011920929</v>
@@ -64301,7 +64648,7 @@
         <v>1.1840000152587891</v>
       </c>
       <c r="GW119" s="1">
-        <v>0.034000001847743988</v>
+        <v>3.4000001847743988E-2</v>
       </c>
       <c r="GX119" s="1">
         <v>26.148750305175781</v>
@@ -64313,7 +64660,7 @@
         <v>16</v>
       </c>
       <c r="HA119" s="1">
-        <v>0.2857142984867096</v>
+        <v>0.28571429848670959</v>
       </c>
       <c r="HB119" s="1">
         <v>1</v>
@@ -64322,10 +64669,10 @@
         <v>122</v>
       </c>
       <c r="HD119" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>15</v>
       </c>
@@ -64823,32 +65170,32 @@
         <v>944</v>
       </c>
       <c r="FS120" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT120" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="FU120" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="FV120" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="FW120" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="FX120" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="FY120" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="FZ120" s="1"/>
       <c r="GA120" s="1">
         <v>2025</v>
       </c>
       <c r="GB120" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="GC120" t="s">
         <v>941</v>
@@ -64932,10 +65279,10 @@
         <v>123</v>
       </c>
       <c r="HD120" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1</v>
       </c>
@@ -65415,32 +65762,32 @@
         <v>944</v>
       </c>
       <c r="FS121" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT121" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="FU121" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="FV121" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="FW121" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="FX121" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="FY121" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="FZ121" s="1"/>
       <c r="GA121" s="1">
         <v>2024</v>
       </c>
       <c r="GB121" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="GC121" t="s">
         <v>941</v>
@@ -65524,10 +65871,10 @@
         <v>123</v>
       </c>
       <c r="HD121" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -65853,32 +66200,32 @@
         <v>944</v>
       </c>
       <c r="FS122" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT122" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU122" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="FV122" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="FW122" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="FX122" t="s">
         <v>124</v>
       </c>
       <c r="FY122" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="FZ122" s="1"/>
       <c r="GA122" s="1">
         <v>2025</v>
       </c>
       <c r="GB122" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="GC122" t="s">
         <v>941</v>
@@ -65926,7 +66273,7 @@
         <v>0.2669999897480011</v>
       </c>
       <c r="GR122" s="1">
-        <v>0.068999998271465302</v>
+        <v>6.8999998271465302E-2</v>
       </c>
       <c r="GS122" s="1">
         <v>150.24400329589844</v>
@@ -65941,7 +66288,7 @@
         <v>0.96200001239776611</v>
       </c>
       <c r="GW122" s="1">
-        <v>0.064000003039836884</v>
+        <v>6.4000003039836884E-2</v>
       </c>
       <c r="GX122" s="1">
         <v>25.07090950012207</v>
@@ -65953,7 +66300,7 @@
         <v>4</v>
       </c>
       <c r="HA122" s="1">
-        <v>0.072727270424365997</v>
+        <v>7.2727270424365997E-2</v>
       </c>
       <c r="HB122" s="1">
         <v>1</v>
@@ -65962,10 +66309,10 @@
         <v>124</v>
       </c>
       <c r="HD122" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1</v>
       </c>
@@ -66277,32 +66624,32 @@
         <v>944</v>
       </c>
       <c r="FS123" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT123" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU123" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="FV123" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="FW123" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="FX123" t="s">
         <v>124</v>
       </c>
       <c r="FY123" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="FZ123" s="1"/>
       <c r="GA123" s="1">
         <v>2024</v>
       </c>
       <c r="GB123" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="GC123" t="s">
         <v>941</v>
@@ -66350,7 +66697,7 @@
         <v>0.36300000548362732</v>
       </c>
       <c r="GR123" s="1">
-        <v>0.087999999523162842</v>
+        <v>8.7999999523162842E-2</v>
       </c>
       <c r="GS123" s="1">
         <v>219.57600402832031</v>
@@ -66365,7 +66712,7 @@
         <v>0.87400001287460327</v>
       </c>
       <c r="GW123" s="1">
-        <v>0.05299999937415123</v>
+        <v>5.299999937415123E-2</v>
       </c>
       <c r="GX123" s="1">
         <v>21.652143478393555</v>
@@ -66377,7 +66724,7 @@
         <v>4</v>
       </c>
       <c r="HA123" s="1">
-        <v>0.05714285746216774</v>
+        <v>5.714285746216774E-2</v>
       </c>
       <c r="HB123" s="1">
         <v>1</v>
@@ -66386,10 +66733,10 @@
         <v>124</v>
       </c>
       <c r="HD123" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>30</v>
       </c>
@@ -66715,32 +67062,32 @@
         <v>944</v>
       </c>
       <c r="FS124" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT124" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU124" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="FV124" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="FW124" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="FX124" t="s">
         <v>125</v>
       </c>
       <c r="FY124" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="FZ124" s="1"/>
       <c r="GA124" s="1">
         <v>2025</v>
       </c>
       <c r="GB124" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="GC124" t="s">
         <v>941</v>
@@ -66782,13 +67129,13 @@
         <v>0.9309999942779541</v>
       </c>
       <c r="GP124" s="1">
-        <v>0.85399997234344483</v>
+        <v>0.85399997234344482</v>
       </c>
       <c r="GQ124" s="1">
         <v>0.59700000286102295</v>
       </c>
       <c r="GR124" s="1">
-        <v>0.079000003635883331</v>
+        <v>7.9000003635883331E-2</v>
       </c>
       <c r="GS124" s="1">
         <v>456.12100219726563</v>
@@ -66815,7 +67162,7 @@
         <v>11</v>
       </c>
       <c r="HA124" s="1">
-        <v>0.08461538702249527</v>
+        <v>8.461538702249527E-2</v>
       </c>
       <c r="HB124" s="1">
         <v>2</v>
@@ -66824,10 +67171,10 @@
         <v>125</v>
       </c>
       <c r="HD124" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1</v>
       </c>
@@ -67307,32 +67654,32 @@
         <v>944</v>
       </c>
       <c r="FS125" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="FT125" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="FU125" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="FV125" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="FW125" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="FX125" t="s">
         <v>125</v>
       </c>
       <c r="FY125" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="FZ125" s="1"/>
       <c r="GA125" s="1">
         <v>2024</v>
       </c>
       <c r="GB125" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="GC125" t="s">
         <v>941</v>
@@ -67374,13 +67721,13 @@
         <v>0.8410000205039978</v>
       </c>
       <c r="GP125" s="1">
-        <v>0.67900002002716065</v>
+        <v>0.67900002002716064</v>
       </c>
       <c r="GQ125" s="1">
         <v>0.52499997615814209</v>
       </c>
       <c r="GR125" s="1">
-        <v>0.075000002980232239</v>
+        <v>7.5000002980232239E-2</v>
       </c>
       <c r="GS125" s="1">
         <v>429.04800415039063</v>
@@ -67407,7 +67754,7 @@
         <v>9</v>
       </c>
       <c r="HA125" s="1">
-        <v>0.073170728981494904</v>
+        <v>7.3170728981494904E-2</v>
       </c>
       <c r="HB125" s="1">
         <v>2</v>
@@ -67416,10 +67763,10 @@
         <v>125</v>
       </c>
       <c r="HD125" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>2</v>
       </c>
@@ -67745,19 +68092,19 @@
         <v>944</v>
       </c>
       <c r="FS126" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="FT126" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="FU126" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="FV126" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="FW126" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="FX126" t="s">
         <v>126</v>
@@ -67770,7 +68117,7 @@
         <v>2025</v>
       </c>
       <c r="GB126" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="GC126" t="s">
         <v>941</v>
@@ -67812,13 +68159,13 @@
         <v>0.76399999856948853</v>
       </c>
       <c r="GP126" s="1">
-        <v>0.57899999618530274</v>
+        <v>0.57899999618530273</v>
       </c>
       <c r="GQ126" s="1">
         <v>0.36300000548362732</v>
       </c>
       <c r="GR126" s="1">
-        <v>0.086000002920627594</v>
+        <v>8.6000002920627594E-2</v>
       </c>
       <c r="GS126" s="1">
         <v>336.75201416015625</v>
@@ -67833,7 +68180,7 @@
         <v>0.89499998092651367</v>
       </c>
       <c r="GW126" s="1">
-        <v>0.032000001519918442</v>
+        <v>3.2000001519918442E-2</v>
       </c>
       <c r="GX126" s="1">
         <v>16.440475463867188</v>
@@ -67854,10 +68201,10 @@
         <v>126</v>
       </c>
       <c r="HD126" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1</v>
       </c>
@@ -68173,19 +68520,19 @@
         <v>944</v>
       </c>
       <c r="FS127" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="FT127" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="FU127" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="FV127" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="FW127" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="FX127" t="s">
         <v>126</v>
@@ -68198,7 +68545,7 @@
         <v>2024</v>
       </c>
       <c r="GB127" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="GC127" t="s">
         <v>941</v>
@@ -68261,7 +68608,7 @@
         <v>2.5759999752044678</v>
       </c>
       <c r="GW127" s="1">
-        <v>0.064999997615814209</v>
+        <v>6.4999997615814209E-2</v>
       </c>
       <c r="GX127" s="1">
         <v>16.10040283203125</v>
@@ -68282,10 +68629,10 @@
         <v>126</v>
       </c>
       <c r="HD127" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -68611,32 +68958,32 @@
         <v>944</v>
       </c>
       <c r="FS128" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT128" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU128" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="FV128" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="FW128" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="FX128" t="s">
         <v>128</v>
       </c>
       <c r="FY128" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="FZ128" s="1"/>
       <c r="GA128" s="1">
         <v>2025</v>
       </c>
       <c r="GB128" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="GC128" t="s">
         <v>941</v>
@@ -68699,7 +69046,7 @@
         <v>1.1180000305175781</v>
       </c>
       <c r="GW128" s="1">
-        <v>0.057999998331069946</v>
+        <v>5.7999998331069946E-2</v>
       </c>
       <c r="GX128" s="1">
         <v>17.514034271240234</v>
@@ -68720,10 +69067,10 @@
         <v>128</v>
       </c>
       <c r="HD128" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1</v>
       </c>
@@ -68981,7 +69328,7 @@
         <v>0</v>
       </c>
       <c r="EY129" s="1">
-        <v>1.0005555152893067</v>
+        <v>1.0005555152893066</v>
       </c>
       <c r="EZ129" t="s">
         <v>524</v>
@@ -69039,32 +69386,32 @@
         <v>944</v>
       </c>
       <c r="FS129" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="FT129" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="FU129" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="FV129" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="FW129" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="FX129" t="s">
         <v>128</v>
       </c>
       <c r="FY129" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="FZ129" s="1"/>
       <c r="GA129" s="1">
         <v>2024</v>
       </c>
       <c r="GB129" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="GC129" t="s">
         <v>941</v>
@@ -69127,7 +69474,7 @@
         <v>1.2829999923706055</v>
       </c>
       <c r="GW129" s="1">
-        <v>0.054999999701976776</v>
+        <v>5.4999999701976776E-2</v>
       </c>
       <c r="GX129" s="1">
         <v>18.282951354980469</v>
@@ -69139,7 +69486,7 @@
         <v>6</v>
       </c>
       <c r="HA129" s="1">
-        <v>0.098360657691955567</v>
+        <v>9.8360657691955566E-2</v>
       </c>
       <c r="HB129" s="1">
         <v>1</v>
@@ -69148,10 +69495,10 @@
         <v>128</v>
       </c>
       <c r="HD129" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1</v>
       </c>
@@ -69558,7 +69905,7 @@
         <v>14.229999542236328</v>
       </c>
       <c r="ET130" s="1">
-        <v>5.1500000953674317</v>
+        <v>5.1500000953674316</v>
       </c>
       <c r="EU130" s="1">
         <v>3</v>
@@ -69631,32 +69978,32 @@
         <v>944</v>
       </c>
       <c r="FS130" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT130" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="FU130" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="FV130" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="FW130" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="FX130" t="s">
         <v>130</v>
       </c>
       <c r="FY130" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="FZ130" s="1"/>
       <c r="GA130" s="1">
         <v>2024</v>
       </c>
       <c r="GB130" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="GC130" t="s">
         <v>941</v>
@@ -69698,7 +70045,7 @@
         <v>0.75900000333786011</v>
       </c>
       <c r="GP130" s="1">
-        <v>0.546999990940094</v>
+        <v>0.54699999094009399</v>
       </c>
       <c r="GQ130" s="1">
         <v>0.44600000977516174</v>
@@ -69719,7 +70066,7 @@
         <v>1.5640000104904175</v>
       </c>
       <c r="GW130" s="1">
-        <v>0.054999999701976776</v>
+        <v>5.4999999701976776E-2</v>
       </c>
       <c r="GX130" s="1">
         <v>25.303789138793945</v>
@@ -69740,10 +70087,10 @@
         <v>130</v>
       </c>
       <c r="HD130" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>22</v>
       </c>
@@ -70239,32 +70586,32 @@
         <v>944</v>
       </c>
       <c r="FS131" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="FT131" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="FU131" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="FV131" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="FW131" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="FX131" t="s">
         <v>130</v>
       </c>
       <c r="FY131" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="FZ131" s="1"/>
       <c r="GA131" s="1">
         <v>2025</v>
       </c>
       <c r="GB131" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="GC131" t="s">
         <v>941</v>
@@ -70324,10 +70671,10 @@
         <v>11.539999961853027</v>
       </c>
       <c r="GV131" s="1">
-        <v>0.99000000953674317</v>
+        <v>0.99000000953674316</v>
       </c>
       <c r="GW131" s="1">
-        <v>0.035000000149011612</v>
+        <v>3.5000000149011612E-2</v>
       </c>
       <c r="GX131" s="1">
         <v>24.238765716552734</v>
@@ -70348,10 +70695,10 @@
         <v>130</v>
       </c>
       <c r="HD131" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1</v>
       </c>
@@ -70641,10 +70988,10 @@
         <v>1</v>
       </c>
       <c r="FS132" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT132" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="FU132" t="s">
         <v>1</v>
@@ -70695,13 +71042,13 @@
       <c r="HA132" s="1"/>
       <c r="HB132" s="1"/>
       <c r="HC132" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="HD132" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1</v>
       </c>
@@ -70981,10 +71328,10 @@
         <v>1</v>
       </c>
       <c r="FS133" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="FT133" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="FU133" t="s">
         <v>1</v>
@@ -71035,13 +71382,13 @@
       <c r="HA133" s="1"/>
       <c r="HB133" s="1"/>
       <c r="HC133" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="HD133" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1</v>
       </c>
@@ -71485,10 +71832,10 @@
         <v>1</v>
       </c>
       <c r="FS134" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT134" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU134" t="s">
         <v>1</v>
@@ -71542,10 +71889,10 @@
         <v>133</v>
       </c>
       <c r="HD134" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:212" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>23</v>
       </c>
@@ -71835,10 +72182,10 @@
         <v>1</v>
       </c>
       <c r="FS135" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="FT135" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="FU135" t="s">
         <v>1</v>
@@ -71892,9 +72239,11 @@
         <v>133</v>
       </c>
       <c r="HD135" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:HD135" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/flagship_dashboard.xlsx
+++ b/flagship_dashboard.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6755" uniqueCount="1451">
   <si>
-    <t>isin</t>
+    <t>ISIN</t>
   </si>
   <si>
     <t>BE0974293251</t>
@@ -219,217 +219,217 @@
     <t>NL0015001WM6</t>
   </si>
   <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>e11</t>
-  </si>
-  <si>
-    <t>e12</t>
-  </si>
-  <si>
-    <t>e13</t>
-  </si>
-  <si>
-    <t>e14</t>
-  </si>
-  <si>
-    <t>e15</t>
-  </si>
-  <si>
-    <t>e16</t>
-  </si>
-  <si>
-    <t>e17</t>
-  </si>
-  <si>
-    <t>e18</t>
-  </si>
-  <si>
-    <t>e19</t>
-  </si>
-  <si>
-    <t>e21</t>
-  </si>
-  <si>
-    <t>e22</t>
-  </si>
-  <si>
-    <t>e23</t>
-  </si>
-  <si>
-    <t>e24</t>
-  </si>
-  <si>
-    <t>e25</t>
-  </si>
-  <si>
-    <t>e26</t>
-  </si>
-  <si>
-    <t>e31</t>
-  </si>
-  <si>
-    <t>e32</t>
-  </si>
-  <si>
-    <t>e33</t>
-  </si>
-  <si>
-    <t>e34</t>
-  </si>
-  <si>
-    <t>e35</t>
-  </si>
-  <si>
-    <t>e41</t>
-  </si>
-  <si>
-    <t>e42</t>
-  </si>
-  <si>
-    <t>e43</t>
-  </si>
-  <si>
-    <t>e44</t>
-  </si>
-  <si>
-    <t>e45</t>
-  </si>
-  <si>
-    <t>e46</t>
-  </si>
-  <si>
-    <t>e51</t>
-  </si>
-  <si>
-    <t>e52</t>
-  </si>
-  <si>
-    <t>e53</t>
-  </si>
-  <si>
-    <t>e54</t>
-  </si>
-  <si>
-    <t>e55</t>
-  </si>
-  <si>
-    <t>e56</t>
-  </si>
-  <si>
-    <t>s11</t>
-  </si>
-  <si>
-    <t>s12</t>
-  </si>
-  <si>
-    <t>s13</t>
-  </si>
-  <si>
-    <t>s14</t>
-  </si>
-  <si>
-    <t>s15</t>
-  </si>
-  <si>
-    <t>s16</t>
-  </si>
-  <si>
-    <t>s17</t>
-  </si>
-  <si>
-    <t>s18</t>
-  </si>
-  <si>
-    <t>s19</t>
-  </si>
-  <si>
-    <t>s110</t>
-  </si>
-  <si>
-    <t>s111</t>
-  </si>
-  <si>
-    <t>s112</t>
-  </si>
-  <si>
-    <t>s113</t>
-  </si>
-  <si>
-    <t>s114</t>
-  </si>
-  <si>
-    <t>s115</t>
-  </si>
-  <si>
-    <t>s116</t>
-  </si>
-  <si>
-    <t>s117</t>
-  </si>
-  <si>
-    <t>s21</t>
-  </si>
-  <si>
-    <t>s22</t>
-  </si>
-  <si>
-    <t>s23</t>
-  </si>
-  <si>
-    <t>s24</t>
-  </si>
-  <si>
-    <t>s25</t>
-  </si>
-  <si>
-    <t>s31</t>
-  </si>
-  <si>
-    <t>s32</t>
-  </si>
-  <si>
-    <t>s33</t>
-  </si>
-  <si>
-    <t>s34</t>
-  </si>
-  <si>
-    <t>s35</t>
-  </si>
-  <si>
-    <t>s41</t>
-  </si>
-  <si>
-    <t>s42</t>
-  </si>
-  <si>
-    <t>s43</t>
-  </si>
-  <si>
-    <t>s44</t>
-  </si>
-  <si>
-    <t>s45</t>
-  </si>
-  <si>
-    <t>g11</t>
-  </si>
-  <si>
-    <t>g12</t>
-  </si>
-  <si>
-    <t>g13</t>
-  </si>
-  <si>
-    <t>g14</t>
-  </si>
-  <si>
-    <t>g15</t>
-  </si>
-  <si>
-    <t>g16</t>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>E1-1</t>
+  </si>
+  <si>
+    <t>E1-2</t>
+  </si>
+  <si>
+    <t>E1-3</t>
+  </si>
+  <si>
+    <t>E1-4</t>
+  </si>
+  <si>
+    <t>E1-5</t>
+  </si>
+  <si>
+    <t>E1-6</t>
+  </si>
+  <si>
+    <t>E1-7</t>
+  </si>
+  <si>
+    <t>E1-8</t>
+  </si>
+  <si>
+    <t>E1-9</t>
+  </si>
+  <si>
+    <t>E2-1</t>
+  </si>
+  <si>
+    <t>E2-2</t>
+  </si>
+  <si>
+    <t>E2-3</t>
+  </si>
+  <si>
+    <t>E2-4</t>
+  </si>
+  <si>
+    <t>E2-5</t>
+  </si>
+  <si>
+    <t>E2-6</t>
+  </si>
+  <si>
+    <t>E3-1</t>
+  </si>
+  <si>
+    <t>E3-2</t>
+  </si>
+  <si>
+    <t>E3-3</t>
+  </si>
+  <si>
+    <t>E3-4</t>
+  </si>
+  <si>
+    <t>E3-5</t>
+  </si>
+  <si>
+    <t>E4-1</t>
+  </si>
+  <si>
+    <t>E4-2</t>
+  </si>
+  <si>
+    <t>E4-3</t>
+  </si>
+  <si>
+    <t>E4-4</t>
+  </si>
+  <si>
+    <t>E4-5</t>
+  </si>
+  <si>
+    <t>E4-6</t>
+  </si>
+  <si>
+    <t>E5-1</t>
+  </si>
+  <si>
+    <t>E5-2</t>
+  </si>
+  <si>
+    <t>E5-3</t>
+  </si>
+  <si>
+    <t>E5-4</t>
+  </si>
+  <si>
+    <t>E5-5</t>
+  </si>
+  <si>
+    <t>E5-6</t>
+  </si>
+  <si>
+    <t>S1-1</t>
+  </si>
+  <si>
+    <t>S1-2</t>
+  </si>
+  <si>
+    <t>S1-3</t>
+  </si>
+  <si>
+    <t>S1-4</t>
+  </si>
+  <si>
+    <t>S1-5</t>
+  </si>
+  <si>
+    <t>S1-6</t>
+  </si>
+  <si>
+    <t>S1-7</t>
+  </si>
+  <si>
+    <t>S1-8</t>
+  </si>
+  <si>
+    <t>S1-9</t>
+  </si>
+  <si>
+    <t>S1-10</t>
+  </si>
+  <si>
+    <t>S1-11</t>
+  </si>
+  <si>
+    <t>S1-12</t>
+  </si>
+  <si>
+    <t>S1-13</t>
+  </si>
+  <si>
+    <t>S1-14</t>
+  </si>
+  <si>
+    <t>S1-15</t>
+  </si>
+  <si>
+    <t>S1-16</t>
+  </si>
+  <si>
+    <t>S1-17</t>
+  </si>
+  <si>
+    <t>S2-1</t>
+  </si>
+  <si>
+    <t>S2-2</t>
+  </si>
+  <si>
+    <t>S2-3</t>
+  </si>
+  <si>
+    <t>S2-4</t>
+  </si>
+  <si>
+    <t>S2-5</t>
+  </si>
+  <si>
+    <t>S3-1</t>
+  </si>
+  <si>
+    <t>S3-2</t>
+  </si>
+  <si>
+    <t>S3-3</t>
+  </si>
+  <si>
+    <t>S3-4</t>
+  </si>
+  <si>
+    <t>S3-5</t>
+  </si>
+  <si>
+    <t>S4-1</t>
+  </si>
+  <si>
+    <t>S4-2</t>
+  </si>
+  <si>
+    <t>S4-3</t>
+  </si>
+  <si>
+    <t>S4-4</t>
+  </si>
+  <si>
+    <t>S4-5</t>
+  </si>
+  <si>
+    <t>G1-1</t>
+  </si>
+  <si>
+    <t>G1-2</t>
+  </si>
+  <si>
+    <t>G1-3</t>
+  </si>
+  <si>
+    <t>G1-4</t>
+  </si>
+  <si>
+    <t>G1-5</t>
+  </si>
+  <si>
+    <t>G1-6</t>
   </si>
   <si>
     <t>publication_date_2025</t>
@@ -561,7 +561,7 @@
     <t>19feb2026</t>
   </si>
   <si>
-    <t>nondecfye</t>
+    <t>non-Dec-FYE</t>
   </si>
   <si>
     <t>name</t>
@@ -939,52 +939,52 @@
     <t>es50</t>
   </si>
   <si>
-    <t>e19_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>e26_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>e35_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>e4fully_phased_in</t>
-  </si>
-  <si>
-    <t>e46_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>e56_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s17_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s18_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s111_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s112_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s113_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s114_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s115_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>s2fully_phased_in</t>
-  </si>
-  <si>
-    <t>s3fully_phased_in</t>
-  </si>
-  <si>
-    <t>s4fully_phased_in</t>
+    <t>E1-9_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E2-6_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E3-5_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E4-fully_phased_in</t>
+  </si>
+  <si>
+    <t>E4-6_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E5-6_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-7_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-8_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-11_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-12_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-13_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-14_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-15_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S2-fully_phased_in</t>
+  </si>
+  <si>
+    <t>S3-fully_phased_in</t>
+  </si>
+  <si>
+    <t>S4-fully_phased_in</t>
   </si>
   <si>
     <t>keep</t>
@@ -999,7 +999,7 @@
     <t>FALSE</t>
   </si>
   <si>
-    <t>country</t>
+    <t>Country</t>
   </si>
   <si>
     <t>BELGIUM</t>
@@ -1035,7 +1035,7 @@
     <t>NETHERLANDS</t>
   </si>
   <si>
-    <t>nontransposer</t>
+    <t>non-transposer</t>
   </si>
   <si>
     <t>No</t>
@@ -2754,7 +2754,7 @@
     <t>2026-02-24T10:05:47.530818+00:00</t>
   </si>
   <si>
-    <t>primary_sics_sector</t>
+    <t>Sector</t>
   </si>
   <si>
     <t>Food &amp; Beverage</t>
@@ -2787,7 +2787,7 @@
     <t>Services</t>
   </si>
   <si>
-    <t>industry</t>
+    <t>Industry</t>
   </si>
   <si>
     <t>Alcoholic Beverages</t>
@@ -3840,7 +3840,7 @@
     <t>date</t>
   </si>
   <si>
-    <t>pages</t>
+    <t>Pages</t>
   </si>
   <si>
     <t>total_words_pos_unscaled</t>
@@ -3909,10 +3909,10 @@
     <t>image_ratio</t>
   </si>
   <si>
-    <t>word_terc</t>
-  </si>
-  <si>
-    <t>company</t>
+    <t xml:space="preserve">3 quantiles of total_words </t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
   <si>
     <t>L’Oréal</t>
@@ -3921,7 +3921,7 @@
     <t>Prosus NV</t>
   </si>
   <si>
-    <t>published</t>
+    <t>Published</t>
   </si>
   <si>
     <t>2026-03-26</t>
@@ -3954,10 +3954,10 @@
     <t>2025-06-23</t>
   </si>
   <si>
-    <t>csrdcompliant</t>
-  </si>
-  <si>
-    <t>reportyear</t>
+    <t>CSRD Compliant</t>
+  </si>
+  <si>
+    <t>Report Year</t>
   </si>
   <si>
     <t>First Year CSRD</t>
@@ -3966,7 +3966,7 @@
     <t>Second Year CSRD</t>
   </si>
   <si>
-    <t>reportlink</t>
+    <t>Report Link</t>
   </si>
   <si>
     <t>https://db.srnav.com/storage/v1/object/public/document-pdfs/05f42eb7-e16f-4824-adec-f4d9ca16443f.pdf#page=145</t>
@@ -4353,7 +4353,7 @@
     <t>https://db.srnav.com/storage/v1/object/public/document-pdfs/6fcd017b-f4b3-44ca-87f3-cdc60cbde444.pdf#page=49</t>
   </si>
   <si>
-    <t>sector_broad</t>
+    <t>Aggregated sector classification</t>
   </si>
   <si>
     <t>Consumer &amp; Health</t>
